--- a/dptest/Templates/Report Templates/Memphis templates/JAWHA/OQC_Report_Memphis_MP_Z Stopper_.xlsx
+++ b/dptest/Templates/Report Templates/Memphis templates/JAWHA/OQC_Report_Memphis_MP_Z Stopper_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user01\Desktop\Memphis templates (2)\Memphis templates\JAWHA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\JTMES\Templates\Report Templates\Memphis templates\JAWHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11BD3B0-C59B-4756-A3F2-4549BCF7910F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6789DB9A-E4A8-4737-B6A5-AC716CFBB804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" tabRatio="792" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
   </bookViews>
   <sheets>
     <sheet name="Waiver Summary" sheetId="5" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="FAI" sheetId="22" r:id="rId3"/>
     <sheet name="SPC" sheetId="23" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="________XG2" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="________XG2" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -2263,7 +2260,7 @@
     <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="2" hidden="1">FAI!ㅂㅂㅂ</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="3" hidden="1">SPC!ㅂㅂㅂ</definedName>
-    <definedName name="ㅂㅂㅂ" hidden="1">[1]!ㅂㅂㅂ</definedName>
+    <definedName name="ㅂㅂㅂ" hidden="1">#REF!</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -6721,87 +6718,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="181" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -6818,10 +6734,96 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="38" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="372">
     <cellStyle name="___CPK__" xfId="52" xr:uid="{66B5D527-70B2-400F-8B63-DFBD3372561C}"/>
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="29" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="33" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="37" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="41" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색1 10" xfId="226" xr:uid="{144ACF6C-EC76-4508-8082-1FFC5044376A}"/>
     <cellStyle name="20% - 강조색1 11" xfId="246" xr:uid="{A0133E03-4FF6-4773-83EB-E1C71755515E}"/>
     <cellStyle name="20% - 강조색1 12" xfId="266" xr:uid="{69765A4B-5601-441F-932C-239E408BA924}"/>
@@ -6837,7 +6839,6 @@
     <cellStyle name="20% - 강조색1 7" xfId="166" xr:uid="{3D432729-A8DE-423D-A1F2-8BB10728B8A7}"/>
     <cellStyle name="20% - 강조색1 8" xfId="186" xr:uid="{EA8B51F4-DF1C-4AD3-B065-82345EB025A5}"/>
     <cellStyle name="20% - 강조색1 9" xfId="206" xr:uid="{3AF2B297-8D3F-4630-89A2-074B4220D709}"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2 10" xfId="229" xr:uid="{626F9513-4C92-4F94-B200-104CF2CD402B}"/>
     <cellStyle name="20% - 강조색2 11" xfId="249" xr:uid="{26249CFF-D7A2-4344-AF21-7004B903DE59}"/>
     <cellStyle name="20% - 강조색2 12" xfId="269" xr:uid="{4C7B131D-BF00-41A3-A47F-EF7251B28828}"/>
@@ -6853,7 +6854,6 @@
     <cellStyle name="20% - 강조색2 7" xfId="169" xr:uid="{3ACEDB0C-3AB5-42A9-8A54-0171BEA68931}"/>
     <cellStyle name="20% - 강조색2 8" xfId="189" xr:uid="{92D06AA7-BD79-4A08-A0AC-19FAAE141A9A}"/>
     <cellStyle name="20% - 강조색2 9" xfId="209" xr:uid="{87FEFB61-F2A8-431E-926D-D0AA74DBDF54}"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3 10" xfId="232" xr:uid="{61651A33-B832-41AE-9EBF-C4749E3E2278}"/>
     <cellStyle name="20% - 강조색3 11" xfId="252" xr:uid="{E949058E-E0C6-4200-8EC6-DBEF142DAD18}"/>
     <cellStyle name="20% - 강조색3 12" xfId="272" xr:uid="{426D12DE-A4BE-4992-808E-7DC40B9718AD}"/>
@@ -6869,7 +6869,6 @@
     <cellStyle name="20% - 강조색3 7" xfId="172" xr:uid="{FBCAFDFA-76DB-42D8-9AFC-73132063C498}"/>
     <cellStyle name="20% - 강조색3 8" xfId="192" xr:uid="{7B7916C4-7649-4B69-BBA1-586F1F8236AC}"/>
     <cellStyle name="20% - 강조색3 9" xfId="212" xr:uid="{B05A3FC1-2BD3-4D5D-BBD1-AF122FFA97D0}"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42" customBuiltin="1"/>
     <cellStyle name="20% - 강조색4 10" xfId="235" xr:uid="{D7777BE9-BACF-476F-AC89-842F95EB340A}"/>
     <cellStyle name="20% - 강조색4 11" xfId="255" xr:uid="{8CECB8CF-16A3-4C86-9941-19EB25997AC4}"/>
     <cellStyle name="20% - 강조색4 12" xfId="275" xr:uid="{11494E53-DE89-497B-B9CA-0A28AD5C723D}"/>
@@ -6885,7 +6884,6 @@
     <cellStyle name="20% - 강조색4 7" xfId="175" xr:uid="{D8023C2B-337C-4793-B1D3-453BF274B485}"/>
     <cellStyle name="20% - 강조색4 8" xfId="195" xr:uid="{8113DDBD-D399-448B-B8ED-873D89E0096A}"/>
     <cellStyle name="20% - 강조색4 9" xfId="215" xr:uid="{14FB7DB9-C519-47BE-8EC1-AA255607A88C}"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - 강조색5 10" xfId="238" xr:uid="{E411D9CE-490D-4DFD-94EE-328AACF8795E}"/>
     <cellStyle name="20% - 강조색5 11" xfId="258" xr:uid="{A182F85F-D434-4461-A92A-139E7B12C467}"/>
     <cellStyle name="20% - 강조색5 12" xfId="278" xr:uid="{EB7F973A-7A61-4F6E-A5B0-410E883B7724}"/>
@@ -6901,7 +6899,6 @@
     <cellStyle name="20% - 강조색5 7" xfId="178" xr:uid="{4E271861-0A9C-4BD9-AA4B-8EC2BC60B6CD}"/>
     <cellStyle name="20% - 강조색5 8" xfId="198" xr:uid="{065D2FA9-1C3F-4C00-BAA7-41A137662E55}"/>
     <cellStyle name="20% - 강조색5 9" xfId="218" xr:uid="{772F6110-8CBC-401D-913D-DFF9BBD2E526}"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색6 10" xfId="241" xr:uid="{A9D7E7EF-A19E-4C1A-AB1C-96A3CDA2DCD8}"/>
     <cellStyle name="20% - 강조색6 11" xfId="261" xr:uid="{8D2F71CB-6051-471E-94A7-4CAE37718795}"/>
     <cellStyle name="20% - 강조색6 12" xfId="281" xr:uid="{2976DA9E-E40C-4CBB-B753-8F3838D90FF5}"/>
@@ -6917,7 +6914,12 @@
     <cellStyle name="20% - 강조색6 7" xfId="181" xr:uid="{7F0E0991-186C-46D1-849C-F961850DAF91}"/>
     <cellStyle name="20% - 강조색6 8" xfId="201" xr:uid="{25052CED-D218-4512-8F9B-138DD7092BA0}"/>
     <cellStyle name="20% - 강조색6 9" xfId="221" xr:uid="{CE3D1595-0958-48A2-B9EE-416DA293B80D}"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="30" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="34" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="38" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="42" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색1 10" xfId="227" xr:uid="{E08ED7FC-FA6B-4FD9-A116-0BE127A8255A}"/>
     <cellStyle name="40% - 강조색1 11" xfId="247" xr:uid="{1995D369-4950-4911-8B5B-D6D1B63DABEC}"/>
     <cellStyle name="40% - 강조색1 12" xfId="267" xr:uid="{28FA5F6C-C506-48F5-972A-4BD8254ECA20}"/>
@@ -6933,7 +6935,6 @@
     <cellStyle name="40% - 강조색1 7" xfId="167" xr:uid="{1927FD0E-4BE2-4492-BB2E-1966527C7123}"/>
     <cellStyle name="40% - 강조색1 8" xfId="187" xr:uid="{534FA0DC-8F7C-49E0-9E23-7705211A8717}"/>
     <cellStyle name="40% - 강조색1 9" xfId="207" xr:uid="{3AE69E2A-7B92-4C93-BFD7-548085599299}"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35" customBuiltin="1"/>
     <cellStyle name="40% - 강조색2 10" xfId="230" xr:uid="{382D258B-D946-495B-BB96-23BC5A2A4906}"/>
     <cellStyle name="40% - 강조색2 11" xfId="250" xr:uid="{BCC6833B-7F37-4366-AB03-A4189D5D1A5C}"/>
     <cellStyle name="40% - 강조색2 12" xfId="270" xr:uid="{403E36EF-A38B-4C19-8BA7-DB8475CFAFF4}"/>
@@ -6949,7 +6950,6 @@
     <cellStyle name="40% - 강조색2 7" xfId="170" xr:uid="{06D71241-9842-4FB1-92CC-B4734351DE63}"/>
     <cellStyle name="40% - 강조색2 8" xfId="190" xr:uid="{E4CD3BF1-0702-4D79-8779-88F0FB3618AE}"/>
     <cellStyle name="40% - 강조색2 9" xfId="210" xr:uid="{132DE09A-2130-4280-B94F-352BF1679BB9}"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39" customBuiltin="1"/>
     <cellStyle name="40% - 강조색3 10" xfId="233" xr:uid="{5DCA0145-145D-477F-9C69-0E7D0BDAA8CE}"/>
     <cellStyle name="40% - 강조색3 11" xfId="253" xr:uid="{12DE31AC-58EA-478B-B2F8-EC3A4EF8B964}"/>
     <cellStyle name="40% - 강조색3 12" xfId="273" xr:uid="{4D7B6B2B-88B6-4009-9330-B8230883E09C}"/>
@@ -6965,7 +6965,6 @@
     <cellStyle name="40% - 강조색3 7" xfId="173" xr:uid="{31D59DE3-E49F-462A-9662-80189E92696D}"/>
     <cellStyle name="40% - 강조색3 8" xfId="193" xr:uid="{B9B7443B-9F0E-4C88-B960-D2AFA151E97E}"/>
     <cellStyle name="40% - 강조색3 9" xfId="213" xr:uid="{4A23610B-77CE-47A2-B2FB-E8C44A920724}"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43" customBuiltin="1"/>
     <cellStyle name="40% - 강조색4 10" xfId="236" xr:uid="{279AACC2-5F8A-4635-BD30-C38CC99F5BBF}"/>
     <cellStyle name="40% - 강조색4 11" xfId="256" xr:uid="{9192174F-5DD8-40D2-8FBE-748F54596A66}"/>
     <cellStyle name="40% - 강조색4 12" xfId="276" xr:uid="{E7D5EA16-D63E-4C1A-AF42-E59203C3D5BE}"/>
@@ -6981,7 +6980,6 @@
     <cellStyle name="40% - 강조색4 7" xfId="176" xr:uid="{45C0AF15-E90B-4919-B72B-1328E7C285F5}"/>
     <cellStyle name="40% - 강조색4 8" xfId="196" xr:uid="{42FE4E23-137F-4281-896F-4A37A35DF536}"/>
     <cellStyle name="40% - 강조색4 9" xfId="216" xr:uid="{5FE4A7DD-4F23-4F4B-9A91-26CA02F74E9F}"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47" customBuiltin="1"/>
     <cellStyle name="40% - 강조색5 10" xfId="239" xr:uid="{BA76548E-7B5B-498D-8406-8634949E5754}"/>
     <cellStyle name="40% - 강조색5 11" xfId="259" xr:uid="{424F185F-7460-4E6C-A653-EFCCE0B5C804}"/>
     <cellStyle name="40% - 강조색5 12" xfId="279" xr:uid="{F5BD1F5E-3484-4B88-A4B4-9A38BB4DB575}"/>
@@ -6997,7 +6995,6 @@
     <cellStyle name="40% - 강조색5 7" xfId="179" xr:uid="{0E855858-D7BA-4E58-A50B-DF778967EFAA}"/>
     <cellStyle name="40% - 강조색5 8" xfId="199" xr:uid="{4D7F1574-D752-49B6-892C-7686097E072D}"/>
     <cellStyle name="40% - 강조색5 9" xfId="219" xr:uid="{C3599F2D-029D-43AC-A322-099F96CB9902}"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색6 10" xfId="242" xr:uid="{E82BFB48-84FD-41B7-AB7F-3FC7DAD9B6DF}"/>
     <cellStyle name="40% - 강조색6 11" xfId="262" xr:uid="{7F222311-21F8-4F52-86D3-B6BCB9F92164}"/>
     <cellStyle name="40% - 강조색6 12" xfId="282" xr:uid="{620521F1-AF1F-4213-A635-B81EA35B4D80}"/>
@@ -7013,7 +7010,12 @@
     <cellStyle name="40% - 강조색6 7" xfId="182" xr:uid="{05CFEC58-67B0-46E3-A580-AB3F892F5F02}"/>
     <cellStyle name="40% - 강조색6 8" xfId="202" xr:uid="{3DB6A435-9D18-41C8-A80C-5CA6BC3C8EC3}"/>
     <cellStyle name="40% - 강조색6 9" xfId="222" xr:uid="{437FDFC9-C82F-4230-A465-4560C5905C74}"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="31" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="35" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="39" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="43" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색1 10" xfId="228" xr:uid="{B2CB40AD-4A4F-4918-9765-E0E0363F2909}"/>
     <cellStyle name="60% - 강조색1 11" xfId="248" xr:uid="{E4397767-24DE-4A4E-8808-6EE3AC7ADD6A}"/>
     <cellStyle name="60% - 강조색1 12" xfId="268" xr:uid="{45163B68-6E14-49BA-BFA4-ECA510354E09}"/>
@@ -7029,7 +7031,6 @@
     <cellStyle name="60% - 강조색1 7" xfId="168" xr:uid="{8212DAC3-9A02-42BE-8CA2-BF85CA1F7FF5}"/>
     <cellStyle name="60% - 강조색1 8" xfId="188" xr:uid="{C4DD9030-1D5F-45AE-A9B8-68EA671C2427}"/>
     <cellStyle name="60% - 강조색1 9" xfId="208" xr:uid="{17F085EB-9BA6-42BC-90C0-6F0174349845}"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36" customBuiltin="1"/>
     <cellStyle name="60% - 강조색2 10" xfId="231" xr:uid="{14C597ED-74A6-41A0-B9C3-84CD44CA0D59}"/>
     <cellStyle name="60% - 강조색2 11" xfId="251" xr:uid="{8C1F64DB-16E4-48E9-A735-71A04F737194}"/>
     <cellStyle name="60% - 강조색2 12" xfId="271" xr:uid="{8AF8D59B-02D0-4311-9B00-197848AD0A13}"/>
@@ -7045,7 +7046,6 @@
     <cellStyle name="60% - 강조색2 7" xfId="171" xr:uid="{54B6E76E-4A23-423C-A58F-0036EF4BD218}"/>
     <cellStyle name="60% - 강조색2 8" xfId="191" xr:uid="{CAB13629-03F9-4D57-B12A-3727FBAF4666}"/>
     <cellStyle name="60% - 강조색2 9" xfId="211" xr:uid="{A63107D2-B5A6-4F95-8B93-DE528608944A}"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40" customBuiltin="1"/>
     <cellStyle name="60% - 강조색3 10" xfId="234" xr:uid="{ED75E9BB-902D-42DB-AF09-843CCDFA3E09}"/>
     <cellStyle name="60% - 강조색3 11" xfId="254" xr:uid="{EA1454C4-3A62-4C0E-9767-7776B2D9DF0C}"/>
     <cellStyle name="60% - 강조색3 12" xfId="274" xr:uid="{758273EF-D7DF-41A3-A017-443AF2472E7F}"/>
@@ -7061,7 +7061,6 @@
     <cellStyle name="60% - 강조색3 7" xfId="174" xr:uid="{CC34085C-2DF9-4B63-BC74-48FB0D0B41C0}"/>
     <cellStyle name="60% - 강조색3 8" xfId="194" xr:uid="{92B4DA0C-F19C-4089-8BF9-BBEE225A05A5}"/>
     <cellStyle name="60% - 강조색3 9" xfId="214" xr:uid="{FB8BE683-8343-4BEB-9B06-CDF01B070856}"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - 강조색4 10" xfId="237" xr:uid="{70E89AC4-5EED-43E7-9ED8-EF9FC159426C}"/>
     <cellStyle name="60% - 강조색4 11" xfId="257" xr:uid="{069866A3-60DC-46EA-9CD7-FBE3CA7D5DA3}"/>
     <cellStyle name="60% - 강조색4 12" xfId="277" xr:uid="{D7C60D16-EB4F-4F13-94C9-22FBC38F668A}"/>
@@ -7077,7 +7076,6 @@
     <cellStyle name="60% - 강조색4 7" xfId="177" xr:uid="{98FF8F1B-C298-4C4F-8370-A09AC3F2FFB8}"/>
     <cellStyle name="60% - 강조색4 8" xfId="197" xr:uid="{5C8022D0-2716-4511-BCE5-F749E9A7505F}"/>
     <cellStyle name="60% - 강조색4 9" xfId="217" xr:uid="{398F5B73-4152-4111-A6C1-88930B304A8F}"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 강조색5 10" xfId="240" xr:uid="{A4732F92-E2E7-47F7-8962-09A53158E49E}"/>
     <cellStyle name="60% - 강조색5 11" xfId="260" xr:uid="{833A5587-5E37-4DDD-A9A7-B9B835D4EEC6}"/>
     <cellStyle name="60% - 강조색5 12" xfId="280" xr:uid="{0CF639C7-E6D7-4838-8BD1-2A7DDFC35C69}"/>
@@ -7093,7 +7091,6 @@
     <cellStyle name="60% - 강조색5 7" xfId="180" xr:uid="{B8F7E0E2-4C83-4F44-B59F-356F510E044A}"/>
     <cellStyle name="60% - 강조색5 8" xfId="200" xr:uid="{6D2D570D-EC52-4E0C-B1E9-5D2AB26D118B}"/>
     <cellStyle name="60% - 강조색5 9" xfId="220" xr:uid="{922B3494-236E-4C09-974D-F60AAF6C7BE7}"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색6 10" xfId="243" xr:uid="{45C2A6A0-CD21-437A-82CA-BC3AD53B6A17}"/>
     <cellStyle name="60% - 강조색6 11" xfId="263" xr:uid="{A320767B-703A-471C-8140-F1287F2FFA6B}"/>
     <cellStyle name="60% - 강조색6 12" xfId="283" xr:uid="{089059AD-EDC4-453B-8BF0-CD3801C452E4}"/>
@@ -7127,16 +7124,24 @@
     <cellStyle name="PrePop Currency (0)" xfId="59" xr:uid="{011529D7-C760-4C88-8E9D-F1167D2FE0AB}"/>
     <cellStyle name="Text Indent A" xfId="60" xr:uid="{DBCAAEB4-FCA1-4A86-9E72-4AB119B0DF9B}"/>
     <cellStyle name="Text Indent B" xfId="61" xr:uid="{49B06124-8F30-4376-AF00-ED1364E50F8D}"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="21" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="18" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="14" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="28" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="32" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="36" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="40" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="44" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="15" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="19" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="21" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="18" builtinId="22" customBuiltin="1"/>
     <cellStyle name="나쁨 2" xfId="365" xr:uid="{4ED3288D-E3DB-4489-ADE3-90A1AB80120C}"/>
+    <cellStyle name="良い" xfId="13" builtinId="26" customBuiltin="1"/>
     <cellStyle name="메모 10" xfId="205" xr:uid="{F1E6B1A6-DFCC-43B5-938B-AC4EA38735C0}"/>
     <cellStyle name="메모 11" xfId="225" xr:uid="{96156C23-3B33-4EC6-904C-30CD9C6AE460}"/>
     <cellStyle name="메모 12" xfId="245" xr:uid="{5CB831BA-C7F1-474B-BA74-58288726F36E}"/>
@@ -7155,25 +7160,17 @@
     <cellStyle name="메모 9" xfId="185" xr:uid="{3BDA0B01-7855-47A6-943B-A22238ECF36D}"/>
     <cellStyle name="百分比 3" xfId="2" xr:uid="{D6C95A67-1C7B-404B-8CDF-2921498D764C}"/>
     <cellStyle name="백분율 2" xfId="49" xr:uid="{E41B836F-9572-4D1C-9D74-1056A2A9CD16}"/>
-    <cellStyle name="보통" xfId="15" builtinId="28" customBuiltin="1"/>
     <cellStyle name="보통 2" xfId="366" xr:uid="{7EC43471-86A2-400A-A5A9-BBBBF5CACFAD}"/>
     <cellStyle name="常规 4" xfId="5" xr:uid="{79A5A741-AEC6-8E4D-AD07-F06A72B84B5A}"/>
     <cellStyle name="常规_8364B 2009415" xfId="48" xr:uid="{0B47AFBD-263D-4B7F-B2E7-B395D86BCEE1}"/>
-    <cellStyle name="설명 텍스트" xfId="22" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="22" builtinId="53" customBuiltin="1"/>
     <cellStyle name="쉼표 [0] 2" xfId="7" xr:uid="{404A706B-A3F0-6D4E-AC76-48F566C7C22E}"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="一般 3" xfId="1" xr:uid="{CBDF56BD-CEEB-C64C-84C9-24C904CBE56D}"/>
-    <cellStyle name="입력" xfId="16" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="8" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="9" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="10" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="11" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="12" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="13" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="17" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="入力" xfId="16" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="17" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10" xfId="204" xr:uid="{97A0A5AD-B5E0-4681-B396-4D85486E02B2}"/>
     <cellStyle name="표준 10 2" xfId="369" xr:uid="{12101C8C-6F95-6841-852A-5ABD1CC97689}"/>
     <cellStyle name="표준 11" xfId="224" xr:uid="{DCBD210C-C26C-487C-AAFF-E96EFCCBF417}"/>
@@ -7242,26 +7239,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="1213 Zs"/>
-    </sheetNames>
-    <definedNames>
-      <definedName name="ㅂㅂㅂ"/>
-    </definedNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7299,7 +7280,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7405,7 +7386,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7547,7 +7528,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7557,33 +7538,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A681568-1FAC-2B47-9C47-A4A560421BB4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:J53"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="15"/>
-    <col min="2" max="2" width="13.81640625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" style="15" customWidth="1"/>
-    <col min="4" max="5" width="25.81640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" style="15"/>
-    <col min="8" max="9" width="10.81640625" style="15" customWidth="1"/>
-    <col min="10" max="16384" width="10.81640625" style="15"/>
+    <col min="1" max="1" width="10.77734375" style="15"/>
+    <col min="2" max="2" width="13.77734375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" style="15" customWidth="1"/>
+    <col min="4" max="5" width="25.77734375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="15"/>
+    <col min="8" max="9" width="10.77734375" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="1:10" ht="40.15" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="16.2" customHeight="1">
+    <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -7595,7 +7576,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="16.2" customHeight="1">
+    <row r="4" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="11" t="s">
@@ -7611,7 +7592,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1">
+    <row r="5" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -7629,7 +7610,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="16.2" customHeight="1">
+    <row r="6" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -7698,7 +7679,7 @@
       <c r="E9" s="125">
         <v>0</v>
       </c>
-      <c r="F9" s="130" t="s">
+      <c r="F9" s="134" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="4"/>
@@ -7720,7 +7701,7 @@
         <f>E8</f>
         <v>480</v>
       </c>
-      <c r="F10" s="130"/>
+      <c r="F10" s="134"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -7735,13 +7716,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4"/>
-      <c r="B12" s="131" t="s">
+      <c r="B12" s="135" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -7771,7 +7752,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="10"/>
-      <c r="B14" s="128" t="s">
+      <c r="B14" s="132" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6"/>
@@ -7781,7 +7762,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="10"/>
-      <c r="B15" s="128"/>
+      <c r="B15" s="132"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
       <c r="E15" s="9"/>
@@ -7789,7 +7770,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="10"/>
-      <c r="B16" s="128"/>
+      <c r="B16" s="132"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
       <c r="E16" s="9"/>
@@ -7797,7 +7778,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="10"/>
-      <c r="B17" s="128"/>
+      <c r="B17" s="132"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
       <c r="E17" s="9"/>
@@ -7805,7 +7786,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="10"/>
-      <c r="B18" s="128"/>
+      <c r="B18" s="132"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
       <c r="E18" s="9"/>
@@ -7813,7 +7794,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="10"/>
-      <c r="B19" s="128"/>
+      <c r="B19" s="132"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
       <c r="E19" s="9"/>
@@ -7821,7 +7802,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="10"/>
-      <c r="B20" s="128"/>
+      <c r="B20" s="132"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7"/>
       <c r="E20" s="9"/>
@@ -7829,7 +7810,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="10"/>
-      <c r="B21" s="128"/>
+      <c r="B21" s="132"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7"/>
       <c r="E21" s="9"/>
@@ -7837,7 +7818,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="10"/>
-      <c r="B22" s="128"/>
+      <c r="B22" s="132"/>
       <c r="C22" s="6"/>
       <c r="D22" s="7"/>
       <c r="E22" s="9"/>
@@ -7845,7 +7826,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="10"/>
-      <c r="B23" s="128"/>
+      <c r="B23" s="132"/>
       <c r="C23" s="6"/>
       <c r="D23" s="7"/>
       <c r="E23" s="9"/>
@@ -7853,7 +7834,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="10"/>
-      <c r="B24" s="128" t="s">
+      <c r="B24" s="132" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6"/>
@@ -7863,7 +7844,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="10"/>
-      <c r="B25" s="128"/>
+      <c r="B25" s="132"/>
       <c r="C25" s="6"/>
       <c r="D25" s="13"/>
       <c r="E25" s="18"/>
@@ -7871,7 +7852,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="10"/>
-      <c r="B26" s="128"/>
+      <c r="B26" s="132"/>
       <c r="C26" s="6"/>
       <c r="D26" s="13"/>
       <c r="E26" s="18"/>
@@ -7879,7 +7860,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="16"/>
-      <c r="B27" s="128"/>
+      <c r="B27" s="132"/>
       <c r="C27" s="6"/>
       <c r="D27" s="13"/>
       <c r="E27" s="18"/>
@@ -7887,7 +7868,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="16"/>
-      <c r="B28" s="128"/>
+      <c r="B28" s="132"/>
       <c r="C28" s="6"/>
       <c r="D28" s="13"/>
       <c r="E28" s="18"/>
@@ -7895,7 +7876,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="16"/>
-      <c r="B29" s="128"/>
+      <c r="B29" s="132"/>
       <c r="C29" s="6"/>
       <c r="D29" s="13"/>
       <c r="E29" s="18"/>
@@ -7903,7 +7884,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="16"/>
-      <c r="B30" s="128"/>
+      <c r="B30" s="132"/>
       <c r="C30" s="6"/>
       <c r="D30" s="13"/>
       <c r="E30" s="18"/>
@@ -7911,7 +7892,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="16"/>
-      <c r="B31" s="128"/>
+      <c r="B31" s="132"/>
       <c r="C31" s="6"/>
       <c r="D31" s="13"/>
       <c r="E31" s="18"/>
@@ -7919,7 +7900,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="16"/>
-      <c r="B32" s="128"/>
+      <c r="B32" s="132"/>
       <c r="C32" s="6"/>
       <c r="D32" s="13"/>
       <c r="E32" s="18"/>
@@ -7927,7 +7908,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="16"/>
-      <c r="B33" s="128"/>
+      <c r="B33" s="132"/>
       <c r="C33" s="6"/>
       <c r="D33" s="13"/>
       <c r="E33" s="18"/>
@@ -7935,7 +7916,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="16"/>
-      <c r="B34" s="128" t="s">
+      <c r="B34" s="132" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="6"/>
@@ -7945,7 +7926,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="16"/>
-      <c r="B35" s="128"/>
+      <c r="B35" s="132"/>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -7953,7 +7934,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="16"/>
-      <c r="B36" s="128"/>
+      <c r="B36" s="132"/>
       <c r="C36" s="6"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -7961,7 +7942,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="16"/>
-      <c r="B37" s="128"/>
+      <c r="B37" s="132"/>
       <c r="C37" s="6"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -7969,7 +7950,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="16"/>
-      <c r="B38" s="128"/>
+      <c r="B38" s="132"/>
       <c r="C38" s="6"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -7977,7 +7958,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="16"/>
-      <c r="B39" s="128"/>
+      <c r="B39" s="132"/>
       <c r="C39" s="6"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -7985,7 +7966,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="16"/>
-      <c r="B40" s="128"/>
+      <c r="B40" s="132"/>
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -7993,7 +7974,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="16"/>
-      <c r="B41" s="128"/>
+      <c r="B41" s="132"/>
       <c r="C41" s="6"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -8001,7 +7982,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="16"/>
-      <c r="B42" s="128"/>
+      <c r="B42" s="132"/>
       <c r="C42" s="6"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -8009,14 +7990,14 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="16"/>
-      <c r="B43" s="128"/>
+      <c r="B43" s="132"/>
       <c r="C43" s="6"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="13"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="B44" s="127" t="s">
+      <c r="B44" s="131" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="6"/>
@@ -8025,63 +8006,63 @@
       <c r="F44" s="13"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="B45" s="127"/>
+      <c r="B45" s="131"/>
       <c r="C45" s="6"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="B46" s="127"/>
+      <c r="B46" s="131"/>
       <c r="C46" s="6"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="13"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="127"/>
+      <c r="B47" s="131"/>
       <c r="C47" s="6"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="13"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="B48" s="127"/>
+      <c r="B48" s="131"/>
       <c r="C48" s="6"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="13"/>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="127"/>
+      <c r="B49" s="131"/>
       <c r="C49" s="6"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="13"/>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="127"/>
+      <c r="B50" s="131"/>
       <c r="C50" s="6"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="13"/>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="127"/>
+      <c r="B51" s="131"/>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="13"/>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="127"/>
+      <c r="B52" s="131"/>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="13"/>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="127"/>
+      <c r="B53" s="131"/>
       <c r="C53" s="6"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -8106,16 +8087,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E15028-B29C-B64B-87D8-5E0B4DDE55A4}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="2" width="17.6328125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="40.6328125" style="43" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="43" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="44" customWidth="1"/>
-    <col min="8" max="9" width="12.6328125" style="43" customWidth="1"/>
-    <col min="10" max="16384" width="10.90625" style="43"/>
+    <col min="1" max="2" width="17.6640625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="40.6640625" style="43" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="44" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" style="43" customWidth="1"/>
+    <col min="10" max="16384" width="10.88671875" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8147,7 +8128,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.2" customHeight="1">
+    <row r="2" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A2" s="111" t="s">
         <v>100</v>
       </c>
@@ -8219,41 +8200,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5FD790-95F8-3D42-B752-B4A6DBB3509E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:T83"/>
-  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="21" customWidth="1"/>
     <col min="2" max="2" width="9" style="21" customWidth="1"/>
     <col min="3" max="3" width="13" style="21" customWidth="1"/>
     <col min="4" max="18" width="9" style="21" customWidth="1"/>
-    <col min="19" max="19" width="13.81640625" style="21" customWidth="1"/>
-    <col min="20" max="20" width="12.453125" style="119"/>
-    <col min="21" max="16384" width="12.453125" style="21"/>
+    <col min="19" max="19" width="13.77734375" style="21" customWidth="1"/>
+    <col min="20" max="20" width="12.44140625" style="119"/>
+    <col min="21" max="16384" width="12.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21">
-      <c r="A1" s="132" t="s">
+    <row r="1" spans="1:19" ht="20.25">
+      <c r="A1" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-    </row>
-    <row r="2" spans="1:19" ht="10.199999999999999" customHeight="1">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+    </row>
+    <row r="2" spans="1:19" ht="10.15" customHeight="1">
       <c r="A2" s="20"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -8276,64 +8257,64 @@
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
       <c r="A3" s="42"/>
-      <c r="B3" s="133" t="s">
+      <c r="B3" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="134" t="s">
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="135" t="s">
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="136"/>
-      <c r="S3" s="137" t="s">
+      <c r="O3" s="138"/>
+      <c r="P3" s="138"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="140"/>
+      <c r="S3" s="141" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
       <c r="A4" s="22"/>
-      <c r="B4" s="137" t="s">
+      <c r="B4" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="138" t="s">
+      <c r="D4" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="139" t="s">
+      <c r="E4" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="139" t="s">
+      <c r="F4" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="142" t="s">
+      <c r="G4" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="143" t="s">
+      <c r="H4" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="144" t="s">
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="143"/>
-      <c r="M4" s="143"/>
-      <c r="N4" s="140" t="s">
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="144" t="s">
         <v>38</v>
       </c>
       <c r="O4" s="23" t="s">
@@ -8344,16 +8325,16 @@
         <v>40</v>
       </c>
       <c r="R4" s="24"/>
-      <c r="S4" s="137"/>
+      <c r="S4" s="141"/>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1">
       <c r="A5" s="26"/>
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="138"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="142"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="146"/>
       <c r="H5" s="41"/>
       <c r="I5" s="41"/>
       <c r="J5" s="41"/>
@@ -8366,7 +8347,7 @@
       <c r="M5" s="41">
         <v>3</v>
       </c>
-      <c r="N5" s="141"/>
+      <c r="N5" s="145"/>
       <c r="O5" s="32" t="s">
         <v>41</v>
       </c>
@@ -8379,7 +8360,7 @@
       <c r="R5" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="137"/>
+      <c r="S5" s="141"/>
     </row>
     <row r="6" spans="1:19" ht="18" customHeight="1">
       <c r="A6" s="27"/>
@@ -8389,13 +8370,13 @@
       <c r="C6" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="154">
+      <c r="D6" s="127">
         <v>0</v>
       </c>
-      <c r="E6" s="154">
+      <c r="E6" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F6" s="154">
+      <c r="F6" s="127">
         <v>0</v>
       </c>
       <c r="G6" s="34" t="s">
@@ -8446,13 +8427,13 @@
       <c r="C7" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="154">
+      <c r="D7" s="127">
         <v>2.0649999999999999</v>
       </c>
-      <c r="E7" s="154">
+      <c r="E7" s="127">
         <v>0.04</v>
       </c>
-      <c r="F7" s="154">
+      <c r="F7" s="127">
         <v>-0.02</v>
       </c>
       <c r="G7" s="34" t="s">
@@ -8503,13 +8484,13 @@
       <c r="C8" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="154">
+      <c r="D8" s="127">
         <v>2.0649999999999999</v>
       </c>
-      <c r="E8" s="154">
+      <c r="E8" s="127">
         <v>0.04</v>
       </c>
-      <c r="F8" s="154">
+      <c r="F8" s="127">
         <v>-0.02</v>
       </c>
       <c r="G8" s="34" t="s">
@@ -8560,13 +8541,13 @@
       <c r="C9" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="154">
+      <c r="D9" s="127">
         <v>2.0649999999999999</v>
       </c>
-      <c r="E9" s="154">
+      <c r="E9" s="127">
         <v>0.04</v>
       </c>
-      <c r="F9" s="154">
+      <c r="F9" s="127">
         <v>-0.02</v>
       </c>
       <c r="G9" s="34" t="s">
@@ -8617,13 +8598,13 @@
       <c r="C10" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="154">
+      <c r="D10" s="127">
         <v>2.0649999999999999</v>
       </c>
-      <c r="E10" s="154">
+      <c r="E10" s="127">
         <v>0.04</v>
       </c>
-      <c r="F10" s="154">
+      <c r="F10" s="127">
         <v>-0.02</v>
       </c>
       <c r="G10" s="34" t="s">
@@ -8674,13 +8655,13 @@
       <c r="C11" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="154">
+      <c r="D11" s="127">
         <v>0.3</v>
       </c>
-      <c r="E11" s="154">
+      <c r="E11" s="127">
         <v>0.03</v>
       </c>
-      <c r="F11" s="154">
+      <c r="F11" s="127">
         <v>-0.03</v>
       </c>
       <c r="G11" s="34" t="s">
@@ -8731,13 +8712,13 @@
       <c r="C12" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="154">
+      <c r="D12" s="127">
         <v>0.3</v>
       </c>
-      <c r="E12" s="154">
+      <c r="E12" s="127">
         <v>0.03</v>
       </c>
-      <c r="F12" s="154">
+      <c r="F12" s="127">
         <v>-0.03</v>
       </c>
       <c r="G12" s="34" t="s">
@@ -8788,13 +8769,13 @@
       <c r="C13" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="154">
+      <c r="D13" s="127">
         <v>0.32</v>
       </c>
-      <c r="E13" s="154">
+      <c r="E13" s="127">
         <v>0.03</v>
       </c>
-      <c r="F13" s="154">
+      <c r="F13" s="127">
         <v>-0.03</v>
       </c>
       <c r="G13" s="34" t="s">
@@ -8845,13 +8826,13 @@
       <c r="C14" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="154">
+      <c r="D14" s="127">
         <v>0.32</v>
       </c>
-      <c r="E14" s="154">
+      <c r="E14" s="127">
         <v>0.03</v>
       </c>
-      <c r="F14" s="154">
+      <c r="F14" s="127">
         <v>-0.03</v>
       </c>
       <c r="G14" s="34" t="s">
@@ -8902,13 +8883,13 @@
       <c r="C15" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="154">
+      <c r="D15" s="127">
         <v>0.1</v>
       </c>
-      <c r="E15" s="154">
+      <c r="E15" s="127">
         <v>0.01</v>
       </c>
-      <c r="F15" s="154">
+      <c r="F15" s="127">
         <v>-0.04</v>
       </c>
       <c r="G15" s="34" t="s">
@@ -8959,13 +8940,13 @@
       <c r="C16" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="154">
+      <c r="D16" s="127">
         <v>0.1</v>
       </c>
-      <c r="E16" s="154">
+      <c r="E16" s="127">
         <v>0.01</v>
       </c>
-      <c r="F16" s="154">
+      <c r="F16" s="127">
         <v>-0.04</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -9016,13 +8997,13 @@
       <c r="C17" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="154">
+      <c r="D17" s="127">
         <v>0.1</v>
       </c>
-      <c r="E17" s="154">
+      <c r="E17" s="127">
         <v>0.01</v>
       </c>
-      <c r="F17" s="154">
+      <c r="F17" s="127">
         <v>-0.04</v>
       </c>
       <c r="G17" s="34" t="s">
@@ -9073,13 +9054,13 @@
       <c r="C18" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="154">
+      <c r="D18" s="127">
         <v>0.1</v>
       </c>
-      <c r="E18" s="154">
+      <c r="E18" s="127">
         <v>0.01</v>
       </c>
-      <c r="F18" s="154">
+      <c r="F18" s="127">
         <v>-0.04</v>
       </c>
       <c r="G18" s="34" t="s">
@@ -9130,13 +9111,13 @@
       <c r="C19" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="154">
+      <c r="D19" s="127">
         <v>90</v>
       </c>
-      <c r="E19" s="154">
+      <c r="E19" s="127">
         <v>1</v>
       </c>
-      <c r="F19" s="154">
+      <c r="F19" s="127">
         <v>-2</v>
       </c>
       <c r="G19" s="34" t="s">
@@ -9187,13 +9168,13 @@
       <c r="C20" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="154">
+      <c r="D20" s="127">
         <v>90</v>
       </c>
-      <c r="E20" s="154">
+      <c r="E20" s="127">
         <v>1</v>
       </c>
-      <c r="F20" s="154">
+      <c r="F20" s="127">
         <v>-2</v>
       </c>
       <c r="G20" s="34" t="s">
@@ -9244,13 +9225,13 @@
       <c r="C21" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="154">
+      <c r="D21" s="127">
         <v>90</v>
       </c>
-      <c r="E21" s="154">
+      <c r="E21" s="127">
         <v>1</v>
       </c>
-      <c r="F21" s="154">
+      <c r="F21" s="127">
         <v>-2</v>
       </c>
       <c r="G21" s="34" t="s">
@@ -9301,13 +9282,13 @@
       <c r="C22" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="154">
+      <c r="D22" s="127">
         <v>90</v>
       </c>
-      <c r="E22" s="154">
+      <c r="E22" s="127">
         <v>1</v>
       </c>
-      <c r="F22" s="154">
+      <c r="F22" s="127">
         <v>-2</v>
       </c>
       <c r="G22" s="34" t="s">
@@ -9358,13 +9339,13 @@
       <c r="C23" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="154">
+      <c r="D23" s="127">
         <v>0.122</v>
       </c>
-      <c r="E23" s="154">
+      <c r="E23" s="127">
         <v>0.01</v>
       </c>
-      <c r="F23" s="154">
+      <c r="F23" s="127">
         <v>-0.02</v>
       </c>
       <c r="G23" s="34" t="s">
@@ -9415,13 +9396,13 @@
       <c r="C24" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="154">
+      <c r="D24" s="127">
         <v>0.122</v>
       </c>
-      <c r="E24" s="154">
+      <c r="E24" s="127">
         <v>0.01</v>
       </c>
-      <c r="F24" s="154">
+      <c r="F24" s="127">
         <v>-0.02</v>
       </c>
       <c r="G24" s="34" t="s">
@@ -9472,13 +9453,13 @@
       <c r="C25" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="154">
+      <c r="D25" s="127">
         <v>7.8E-2</v>
       </c>
-      <c r="E25" s="154">
+      <c r="E25" s="127">
         <v>0.01</v>
       </c>
-      <c r="F25" s="154">
+      <c r="F25" s="127">
         <v>-0.02</v>
       </c>
       <c r="G25" s="34" t="s">
@@ -9529,13 +9510,13 @@
       <c r="C26" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="154">
+      <c r="D26" s="127">
         <v>7.8E-2</v>
       </c>
-      <c r="E26" s="154">
+      <c r="E26" s="127">
         <v>0.01</v>
       </c>
-      <c r="F26" s="154">
+      <c r="F26" s="127">
         <v>-0.02</v>
       </c>
       <c r="G26" s="34" t="s">
@@ -9586,13 +9567,13 @@
       <c r="C27" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="154">
+      <c r="D27" s="127">
         <v>12.494</v>
       </c>
-      <c r="E27" s="154">
+      <c r="E27" s="127">
         <v>0.03</v>
       </c>
-      <c r="F27" s="154">
+      <c r="F27" s="127">
         <v>-0.03</v>
       </c>
       <c r="G27" s="34" t="s">
@@ -9643,13 +9624,13 @@
       <c r="C28" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="154">
+      <c r="D28" s="127">
         <v>0.53300000000000003</v>
       </c>
-      <c r="E28" s="154">
+      <c r="E28" s="127">
         <v>0.03</v>
       </c>
-      <c r="F28" s="154">
+      <c r="F28" s="127">
         <v>-0.03</v>
       </c>
       <c r="G28" s="34" t="s">
@@ -9700,13 +9681,13 @@
       <c r="C29" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="154">
+      <c r="D29" s="127">
         <v>0.53300000000000003</v>
       </c>
-      <c r="E29" s="154">
+      <c r="E29" s="127">
         <v>0.03</v>
       </c>
-      <c r="F29" s="154">
+      <c r="F29" s="127">
         <v>-0.03</v>
       </c>
       <c r="G29" s="34" t="s">
@@ -9757,13 +9738,13 @@
       <c r="C30" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="154">
+      <c r="D30" s="127">
         <v>15.518000000000001</v>
       </c>
-      <c r="E30" s="154">
+      <c r="E30" s="127">
         <v>0.03</v>
       </c>
-      <c r="F30" s="154">
+      <c r="F30" s="127">
         <v>-0.03</v>
       </c>
       <c r="G30" s="34" t="s">
@@ -9814,13 +9795,13 @@
       <c r="C31" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="154">
+      <c r="D31" s="127">
         <v>15.518000000000001</v>
       </c>
-      <c r="E31" s="154">
+      <c r="E31" s="127">
         <v>0.03</v>
       </c>
-      <c r="F31" s="154">
+      <c r="F31" s="127">
         <v>-0.03</v>
       </c>
       <c r="G31" s="34" t="s">
@@ -9871,13 +9852,13 @@
       <c r="C32" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="154">
+      <c r="D32" s="127">
         <v>1.0149999999999999</v>
       </c>
-      <c r="E32" s="154">
+      <c r="E32" s="127">
         <v>0.03</v>
       </c>
-      <c r="F32" s="154">
+      <c r="F32" s="127">
         <v>-0.03</v>
       </c>
       <c r="G32" s="34" t="s">
@@ -9928,13 +9909,13 @@
       <c r="C33" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="154">
+      <c r="D33" s="127">
         <v>14.803000000000001</v>
       </c>
-      <c r="E33" s="154">
+      <c r="E33" s="127">
         <v>0.03</v>
       </c>
-      <c r="F33" s="154">
+      <c r="F33" s="127">
         <v>-0.04</v>
       </c>
       <c r="G33" s="34" t="s">
@@ -9985,13 +9966,13 @@
       <c r="C34" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="154">
+      <c r="D34" s="127">
         <v>11.644</v>
       </c>
-      <c r="E34" s="154">
+      <c r="E34" s="127">
         <v>0.03</v>
       </c>
-      <c r="F34" s="154">
+      <c r="F34" s="127">
         <v>-0.03</v>
       </c>
       <c r="G34" s="34" t="s">
@@ -10036,13 +10017,13 @@
       <c r="C35" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="154">
+      <c r="D35" s="127">
         <v>0.86</v>
       </c>
-      <c r="E35" s="154">
+      <c r="E35" s="127">
         <v>0.03</v>
       </c>
-      <c r="F35" s="154">
+      <c r="F35" s="127">
         <v>-0.03</v>
       </c>
       <c r="G35" s="34" t="s">
@@ -10093,13 +10074,13 @@
       <c r="C36" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="154">
+      <c r="D36" s="127">
         <v>9.9390000000000001</v>
       </c>
-      <c r="E36" s="154">
+      <c r="E36" s="127">
         <v>0.03</v>
       </c>
-      <c r="F36" s="154">
+      <c r="F36" s="127">
         <v>-0.03</v>
       </c>
       <c r="G36" s="34" t="s">
@@ -10150,13 +10131,13 @@
       <c r="C37" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="154">
+      <c r="D37" s="127">
         <v>9.9390000000000001</v>
       </c>
-      <c r="E37" s="154">
+      <c r="E37" s="127">
         <v>0.03</v>
       </c>
-      <c r="F37" s="154">
+      <c r="F37" s="127">
         <v>-0.03</v>
       </c>
       <c r="G37" s="34" t="s">
@@ -10207,13 +10188,13 @@
       <c r="C38" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="154">
+      <c r="D38" s="127">
         <v>0.57499999999999996</v>
       </c>
-      <c r="E38" s="154">
+      <c r="E38" s="127">
         <v>0.03</v>
       </c>
-      <c r="F38" s="154">
+      <c r="F38" s="127">
         <v>-0.03</v>
       </c>
       <c r="G38" s="34" t="s">
@@ -10264,13 +10245,13 @@
       <c r="C39" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D39" s="154">
+      <c r="D39" s="127">
         <v>0.57499999999999996</v>
       </c>
-      <c r="E39" s="154">
+      <c r="E39" s="127">
         <v>0.03</v>
       </c>
-      <c r="F39" s="154">
+      <c r="F39" s="127">
         <v>-0.03</v>
       </c>
       <c r="G39" s="34" t="s">
@@ -10321,13 +10302,13 @@
       <c r="C40" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="154">
+      <c r="D40" s="127">
         <v>1.125</v>
       </c>
-      <c r="E40" s="154">
+      <c r="E40" s="127">
         <v>0.03</v>
       </c>
-      <c r="F40" s="154">
+      <c r="F40" s="127">
         <v>-0.03</v>
       </c>
       <c r="G40" s="34" t="s">
@@ -10378,13 +10359,13 @@
       <c r="C41" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="154">
+      <c r="D41" s="127">
         <v>3.899</v>
       </c>
-      <c r="E41" s="154">
+      <c r="E41" s="127">
         <v>0.03</v>
       </c>
-      <c r="F41" s="154">
+      <c r="F41" s="127">
         <v>-0.03</v>
       </c>
       <c r="G41" s="34" t="s">
@@ -10435,13 +10416,13 @@
       <c r="C42" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="154">
+      <c r="D42" s="127">
         <v>3.899</v>
       </c>
-      <c r="E42" s="154">
+      <c r="E42" s="127">
         <v>0.03</v>
       </c>
-      <c r="F42" s="154">
+      <c r="F42" s="127">
         <v>-0.03</v>
       </c>
       <c r="G42" s="34" t="s">
@@ -10492,13 +10473,13 @@
       <c r="C43" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="154">
+      <c r="D43" s="127">
         <v>4.6340000000000003</v>
       </c>
-      <c r="E43" s="154">
+      <c r="E43" s="127">
         <v>0.03</v>
       </c>
-      <c r="F43" s="154">
+      <c r="F43" s="127">
         <v>-0.03</v>
       </c>
       <c r="G43" s="34" t="s">
@@ -10549,13 +10530,13 @@
       <c r="C44" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="154">
+      <c r="D44" s="127">
         <v>1.01</v>
       </c>
-      <c r="E44" s="154">
+      <c r="E44" s="127">
         <v>0.03</v>
       </c>
-      <c r="F44" s="154">
+      <c r="F44" s="127">
         <v>-0.03</v>
       </c>
       <c r="G44" s="34" t="s">
@@ -10606,13 +10587,13 @@
       <c r="C45" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="154">
+      <c r="D45" s="127">
         <v>11.074</v>
       </c>
-      <c r="E45" s="154">
+      <c r="E45" s="127">
         <v>0.03</v>
       </c>
-      <c r="F45" s="154">
+      <c r="F45" s="127">
         <v>-0.03</v>
       </c>
       <c r="G45" s="34" t="s">
@@ -10663,13 +10644,13 @@
       <c r="C46" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="154">
+      <c r="D46" s="127">
         <v>14.792999999999999</v>
       </c>
-      <c r="E46" s="154">
+      <c r="E46" s="127">
         <v>0.03</v>
       </c>
-      <c r="F46" s="154">
+      <c r="F46" s="127">
         <v>-0.03</v>
       </c>
       <c r="G46" s="34" t="s">
@@ -10720,13 +10701,13 @@
       <c r="C47" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D47" s="154">
+      <c r="D47" s="127">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E47" s="154">
+      <c r="E47" s="127">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F47" s="154">
+      <c r="F47" s="127">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="G47" s="34" t="s">
@@ -10777,13 +10758,13 @@
       <c r="C48" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D48" s="154">
+      <c r="D48" s="127">
         <v>2.17</v>
       </c>
-      <c r="E48" s="154">
+      <c r="E48" s="127">
         <v>0.03</v>
       </c>
-      <c r="F48" s="154">
+      <c r="F48" s="127">
         <v>-0.03</v>
       </c>
       <c r="G48" s="34" t="s">
@@ -10834,13 +10815,13 @@
       <c r="C49" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D49" s="154">
+      <c r="D49" s="127">
         <v>2.17</v>
       </c>
-      <c r="E49" s="154">
+      <c r="E49" s="127">
         <v>0.03</v>
       </c>
-      <c r="F49" s="154">
+      <c r="F49" s="127">
         <v>-0.03</v>
       </c>
       <c r="G49" s="34" t="s">
@@ -10891,13 +10872,13 @@
       <c r="C50" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D50" s="154">
+      <c r="D50" s="127">
         <v>14.343999999999999</v>
       </c>
-      <c r="E50" s="154">
+      <c r="E50" s="127">
         <v>0.03</v>
       </c>
-      <c r="F50" s="154">
+      <c r="F50" s="127">
         <v>-0.03</v>
       </c>
       <c r="G50" s="34" t="s">
@@ -10948,13 +10929,13 @@
       <c r="C51" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D51" s="154">
+      <c r="D51" s="127">
         <v>14.343999999999999</v>
       </c>
-      <c r="E51" s="154">
+      <c r="E51" s="127">
         <v>0.03</v>
       </c>
-      <c r="F51" s="154">
+      <c r="F51" s="127">
         <v>-0.03</v>
       </c>
       <c r="G51" s="34" t="s">
@@ -11005,13 +10986,13 @@
       <c r="C52" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="154">
+      <c r="D52" s="127">
         <v>0.2</v>
       </c>
-      <c r="E52" s="154">
+      <c r="E52" s="127">
         <v>0.04</v>
       </c>
-      <c r="F52" s="154">
+      <c r="F52" s="127">
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="G52" s="34" t="s">
@@ -11062,13 +11043,13 @@
       <c r="C53" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D53" s="154">
+      <c r="D53" s="127">
         <v>0.2</v>
       </c>
-      <c r="E53" s="154">
+      <c r="E53" s="127">
         <v>0.04</v>
       </c>
-      <c r="F53" s="154">
+      <c r="F53" s="127">
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="G53" s="34" t="s">
@@ -11119,13 +11100,13 @@
       <c r="C54" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="154">
+      <c r="D54" s="127">
         <v>1.0900000000000001</v>
       </c>
-      <c r="E54" s="154">
+      <c r="E54" s="127">
         <v>0.03</v>
       </c>
-      <c r="F54" s="154">
+      <c r="F54" s="127">
         <v>-0.03</v>
       </c>
       <c r="G54" s="34" t="s">
@@ -11176,13 +11157,13 @@
       <c r="C55" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D55" s="154">
+      <c r="D55" s="127">
         <v>14.917999999999999</v>
       </c>
-      <c r="E55" s="154">
+      <c r="E55" s="127">
         <v>0.03</v>
       </c>
-      <c r="F55" s="154">
+      <c r="F55" s="127">
         <v>-0.03</v>
       </c>
       <c r="G55" s="34" t="s">
@@ -11233,13 +11214,13 @@
       <c r="C56" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D56" s="154">
+      <c r="D56" s="127">
         <v>1</v>
       </c>
-      <c r="E56" s="154">
+      <c r="E56" s="127">
         <v>0.03</v>
       </c>
-      <c r="F56" s="154">
+      <c r="F56" s="127">
         <v>-0.03</v>
       </c>
       <c r="G56" s="34" t="s">
@@ -11290,13 +11271,13 @@
       <c r="C57" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="154">
+      <c r="D57" s="127">
         <v>0.95</v>
       </c>
-      <c r="E57" s="154">
+      <c r="E57" s="127">
         <v>0.03</v>
       </c>
-      <c r="F57" s="154">
+      <c r="F57" s="127">
         <v>-0.03</v>
       </c>
       <c r="G57" s="34" t="s">
@@ -11347,13 +11328,13 @@
       <c r="C58" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D58" s="154">
+      <c r="D58" s="127">
         <v>2.17</v>
       </c>
-      <c r="E58" s="154">
+      <c r="E58" s="127">
         <v>0.03</v>
       </c>
-      <c r="F58" s="154">
+      <c r="F58" s="127">
         <v>-0.03</v>
       </c>
       <c r="G58" s="34" t="s">
@@ -11404,13 +11385,13 @@
       <c r="C59" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D59" s="154">
+      <c r="D59" s="127">
         <v>2.17</v>
       </c>
-      <c r="E59" s="154">
+      <c r="E59" s="127">
         <v>0.03</v>
       </c>
-      <c r="F59" s="154">
+      <c r="F59" s="127">
         <v>-0.03</v>
       </c>
       <c r="G59" s="34" t="s">
@@ -11461,13 +11442,13 @@
       <c r="C60" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D60" s="154">
+      <c r="D60" s="127">
         <v>12.545999999999999</v>
       </c>
-      <c r="E60" s="154">
+      <c r="E60" s="127">
         <v>0.03</v>
       </c>
-      <c r="F60" s="154">
+      <c r="F60" s="127">
         <v>-0.03</v>
       </c>
       <c r="G60" s="34" t="s">
@@ -11518,13 +11499,13 @@
       <c r="C61" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D61" s="154">
+      <c r="D61" s="127">
         <v>1.2</v>
       </c>
-      <c r="E61" s="154">
+      <c r="E61" s="127">
         <v>0.03</v>
       </c>
-      <c r="F61" s="154">
+      <c r="F61" s="127">
         <v>-0.03</v>
       </c>
       <c r="G61" s="34" t="s">
@@ -11575,13 +11556,13 @@
       <c r="C62" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D62" s="154">
+      <c r="D62" s="127">
         <v>0.99</v>
       </c>
-      <c r="E62" s="154">
+      <c r="E62" s="127">
         <v>0.03</v>
       </c>
-      <c r="F62" s="154">
+      <c r="F62" s="127">
         <v>-0.03</v>
       </c>
       <c r="G62" s="34" t="s">
@@ -11632,13 +11613,13 @@
       <c r="C63" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D63" s="154">
+      <c r="D63" s="127">
         <v>15.042999999999999</v>
       </c>
-      <c r="E63" s="154">
+      <c r="E63" s="127">
         <v>0.03</v>
       </c>
-      <c r="F63" s="154">
+      <c r="F63" s="127">
         <v>-0.04</v>
       </c>
       <c r="G63" s="34" t="s">
@@ -11689,13 +11670,13 @@
       <c r="C64" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D64" s="154">
+      <c r="D64" s="127">
         <v>16.117999999999999</v>
       </c>
-      <c r="E64" s="154">
+      <c r="E64" s="127">
         <v>0.03</v>
       </c>
-      <c r="F64" s="154">
+      <c r="F64" s="127">
         <v>-0.03</v>
       </c>
       <c r="G64" s="34" t="s">
@@ -11746,13 +11727,13 @@
       <c r="C65" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D65" s="154">
+      <c r="D65" s="127">
         <v>16.117999999999999</v>
       </c>
-      <c r="E65" s="154">
+      <c r="E65" s="127">
         <v>0.03</v>
       </c>
-      <c r="F65" s="154">
+      <c r="F65" s="127">
         <v>-0.03</v>
       </c>
       <c r="G65" s="34" t="s">
@@ -11803,13 +11784,13 @@
       <c r="C66" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D66" s="154">
+      <c r="D66" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E66" s="154">
+      <c r="E66" s="127">
         <v>0.03</v>
       </c>
-      <c r="F66" s="154">
+      <c r="F66" s="127">
         <v>-0.03</v>
       </c>
       <c r="G66" s="34" t="s">
@@ -11860,13 +11841,13 @@
       <c r="C67" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D67" s="154">
+      <c r="D67" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E67" s="154">
+      <c r="E67" s="127">
         <v>0.03</v>
       </c>
-      <c r="F67" s="154">
+      <c r="F67" s="127">
         <v>-0.03</v>
       </c>
       <c r="G67" s="34" t="s">
@@ -11917,13 +11898,13 @@
       <c r="C68" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="154">
+      <c r="D68" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E68" s="154">
+      <c r="E68" s="127">
         <v>0.03</v>
       </c>
-      <c r="F68" s="154">
+      <c r="F68" s="127">
         <v>-0.03</v>
       </c>
       <c r="G68" s="34" t="s">
@@ -11974,13 +11955,13 @@
       <c r="C69" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D69" s="154">
+      <c r="D69" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E69" s="154">
+      <c r="E69" s="127">
         <v>0.03</v>
       </c>
-      <c r="F69" s="154">
+      <c r="F69" s="127">
         <v>-0.03</v>
       </c>
       <c r="G69" s="34" t="s">
@@ -12031,13 +12012,13 @@
       <c r="C70" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D70" s="154">
+      <c r="D70" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E70" s="154">
+      <c r="E70" s="127">
         <v>0.03</v>
       </c>
-      <c r="F70" s="154">
+      <c r="F70" s="127">
         <v>-0.03</v>
       </c>
       <c r="G70" s="34" t="s">
@@ -12088,13 +12069,13 @@
       <c r="C71" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D71" s="154">
+      <c r="D71" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E71" s="154">
+      <c r="E71" s="127">
         <v>0.03</v>
       </c>
-      <c r="F71" s="154">
+      <c r="F71" s="127">
         <v>-0.03</v>
       </c>
       <c r="G71" s="34" t="s">
@@ -12145,13 +12126,13 @@
       <c r="C72" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="154">
+      <c r="D72" s="127">
         <v>0.1</v>
       </c>
-      <c r="E72" s="154">
+      <c r="E72" s="127">
         <v>0.01</v>
       </c>
-      <c r="F72" s="154">
+      <c r="F72" s="127">
         <v>-0.04</v>
       </c>
       <c r="G72" s="34" t="s">
@@ -12202,13 +12183,13 @@
       <c r="C73" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D73" s="154">
+      <c r="D73" s="127">
         <v>0.1</v>
       </c>
-      <c r="E73" s="154">
+      <c r="E73" s="127">
         <v>0.01</v>
       </c>
-      <c r="F73" s="154">
+      <c r="F73" s="127">
         <v>-0.04</v>
       </c>
       <c r="G73" s="34" t="s">
@@ -12259,13 +12240,13 @@
       <c r="C74" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D74" s="154">
+      <c r="D74" s="127">
         <v>0.1</v>
       </c>
-      <c r="E74" s="154">
+      <c r="E74" s="127">
         <v>0.01</v>
       </c>
-      <c r="F74" s="154">
+      <c r="F74" s="127">
         <v>-0.04</v>
       </c>
       <c r="G74" s="34" t="s">
@@ -12316,13 +12297,13 @@
       <c r="C75" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D75" s="154">
+      <c r="D75" s="127">
         <v>0.1</v>
       </c>
-      <c r="E75" s="154">
+      <c r="E75" s="127">
         <v>0.01</v>
       </c>
-      <c r="F75" s="154">
+      <c r="F75" s="127">
         <v>-0.04</v>
       </c>
       <c r="G75" s="34" t="s">
@@ -12373,13 +12354,13 @@
       <c r="C76" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="154">
+      <c r="D76" s="127">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E76" s="154">
+      <c r="E76" s="127">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F76" s="154">
+      <c r="F76" s="127">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="G76" s="34" t="s">
@@ -12430,13 +12411,13 @@
       <c r="C77" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D77" s="154">
+      <c r="D77" s="127">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E77" s="154">
+      <c r="E77" s="127">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F77" s="154">
+      <c r="F77" s="127">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="G77" s="34" t="s">
@@ -12487,13 +12468,13 @@
       <c r="C78" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D78" s="154">
+      <c r="D78" s="127">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E78" s="154">
+      <c r="E78" s="127">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F78" s="154">
+      <c r="F78" s="127">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="G78" s="34" t="s">
@@ -12544,13 +12525,13 @@
       <c r="C79" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D79" s="154">
+      <c r="D79" s="127">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E79" s="154">
+      <c r="E79" s="127">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F79" s="154">
+      <c r="F79" s="127">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="G79" s="34" t="s">
@@ -12601,13 +12582,13 @@
       <c r="C80" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D80" s="154">
+      <c r="D80" s="127">
         <v>1.2</v>
       </c>
-      <c r="E80" s="154">
+      <c r="E80" s="127">
         <v>0.03</v>
       </c>
-      <c r="F80" s="154">
+      <c r="F80" s="127">
         <v>-0.03</v>
       </c>
       <c r="G80" s="34" t="s">
@@ -12658,13 +12639,13 @@
       <c r="C81" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D81" s="154">
+      <c r="D81" s="127">
         <v>15.414</v>
       </c>
-      <c r="E81" s="154">
+      <c r="E81" s="127">
         <v>0.24399999999999999</v>
       </c>
-      <c r="F81" s="154">
+      <c r="F81" s="127">
         <v>-0.24399999999999999</v>
       </c>
       <c r="G81" s="34" t="s">
@@ -12715,13 +12696,13 @@
       <c r="C82" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D82" s="154">
+      <c r="D82" s="127">
         <v>6.9189999999999996</v>
       </c>
-      <c r="E82" s="154">
+      <c r="E82" s="127">
         <v>0.3</v>
       </c>
-      <c r="F82" s="154">
+      <c r="F82" s="127">
         <v>-0.3</v>
       </c>
       <c r="G82" s="34" t="s">
@@ -12772,13 +12753,13 @@
       <c r="C83" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D83" s="154">
+      <c r="D83" s="127">
         <v>0</v>
       </c>
-      <c r="E83" s="154">
+      <c r="E83" s="127">
         <v>3</v>
       </c>
-      <c r="F83" s="154">
+      <c r="F83" s="127">
         <v>-3</v>
       </c>
       <c r="G83" s="34" t="s">
@@ -12857,65 +12838,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A5A5CA-E251-C049-A2A7-08038324BBE3}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:BN145"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.81640625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" style="15" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="15" customWidth="1"/>
     <col min="4" max="4" width="24" style="15" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" style="15" customWidth="1"/>
-    <col min="6" max="7" width="8.1796875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="15" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="7.81640625" style="15" customWidth="1"/>
-    <col min="12" max="12" width="0.81640625" style="15" customWidth="1"/>
-    <col min="13" max="16" width="7.81640625" style="15" customWidth="1"/>
-    <col min="17" max="22" width="7.81640625" style="15" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="7.81640625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="15" customWidth="1"/>
+    <col min="6" max="7" width="8.21875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="15" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="7.77734375" style="15" customWidth="1"/>
+    <col min="12" max="12" width="0.77734375" style="15" customWidth="1"/>
+    <col min="13" max="16" width="7.77734375" style="15" customWidth="1"/>
+    <col min="17" max="22" width="7.77734375" style="15" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="7.77734375" style="15" customWidth="1"/>
     <col min="24" max="24" width="10" style="15" hidden="1" customWidth="1"/>
-    <col min="25" max="27" width="9.453125" style="15" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="7.81640625" style="15" customWidth="1"/>
+    <col min="25" max="27" width="9.44140625" style="15" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="7.77734375" style="15" customWidth="1"/>
     <col min="29" max="29" width="9" style="15" customWidth="1"/>
-    <col min="30" max="30" width="8.6328125" style="15" customWidth="1"/>
+    <col min="30" max="30" width="8.6640625" style="15" customWidth="1"/>
     <col min="31" max="32" width="9" style="15" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="7.54296875" style="15" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="0.81640625" style="15" customWidth="1"/>
-    <col min="35" max="66" width="7.81640625" style="15" customWidth="1"/>
-    <col min="67" max="16384" width="8.81640625" style="15"/>
+    <col min="33" max="33" width="7.5546875" style="15" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="0.77734375" style="15" customWidth="1"/>
+    <col min="35" max="66" width="7.77734375" style="15" customWidth="1"/>
+    <col min="67" max="16384" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" s="46" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A1" s="132" t="s">
+    <row r="1" spans="1:66" s="46" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A1" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
-      <c r="U1" s="132"/>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="132"/>
-      <c r="Z1" s="132"/>
-      <c r="AA1" s="132"/>
-      <c r="AB1" s="132"/>
-      <c r="AC1" s="132"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
+      <c r="U1" s="136"/>
+      <c r="V1" s="136"/>
+      <c r="W1" s="136"/>
+      <c r="X1" s="136"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="136"/>
+      <c r="AA1" s="136"/>
+      <c r="AB1" s="136"/>
+      <c r="AC1" s="136"/>
       <c r="AD1" s="20"/>
       <c r="AE1" s="20"/>
       <c r="AF1" s="20"/>
@@ -12960,81 +12941,81 @@
     </row>
     <row r="3" spans="1:66" s="21" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="49"/>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="136"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="140"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="135" t="s">
+      <c r="M3" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="134"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-      <c r="T3" s="134"/>
-      <c r="U3" s="134"/>
-      <c r="V3" s="134"/>
-      <c r="W3" s="134"/>
-      <c r="X3" s="134"/>
-      <c r="Y3" s="134"/>
-      <c r="Z3" s="134"/>
-      <c r="AA3" s="134"/>
-      <c r="AB3" s="134"/>
-      <c r="AC3" s="136"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="138"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="138"/>
+      <c r="T3" s="138"/>
+      <c r="U3" s="138"/>
+      <c r="V3" s="138"/>
+      <c r="W3" s="138"/>
+      <c r="X3" s="138"/>
+      <c r="Y3" s="138"/>
+      <c r="Z3" s="138"/>
+      <c r="AA3" s="138"/>
+      <c r="AB3" s="138"/>
+      <c r="AC3" s="140"/>
       <c r="AD3" s="51"/>
-      <c r="AE3" s="151" t="s">
+      <c r="AE3" s="155" t="s">
         <v>56</v>
       </c>
-      <c r="AF3" s="151"/>
-      <c r="AG3" s="151"/>
+      <c r="AF3" s="155"/>
+      <c r="AG3" s="155"/>
       <c r="AH3" s="52"/>
-      <c r="AI3" s="145" t="s">
+      <c r="AI3" s="149" t="s">
         <v>57</v>
       </c>
-      <c r="AJ3" s="146"/>
-      <c r="AK3" s="146"/>
-      <c r="AL3" s="146"/>
-      <c r="AM3" s="146"/>
-      <c r="AN3" s="146"/>
-      <c r="AO3" s="146"/>
-      <c r="AP3" s="146"/>
-      <c r="AQ3" s="146"/>
-      <c r="AR3" s="146"/>
-      <c r="AS3" s="146"/>
-      <c r="AT3" s="146"/>
-      <c r="AU3" s="146"/>
-      <c r="AV3" s="146"/>
-      <c r="AW3" s="146"/>
-      <c r="AX3" s="146"/>
-      <c r="AY3" s="146"/>
-      <c r="AZ3" s="146"/>
-      <c r="BA3" s="146"/>
-      <c r="BB3" s="146"/>
-      <c r="BC3" s="146"/>
-      <c r="BD3" s="146"/>
-      <c r="BE3" s="146"/>
-      <c r="BF3" s="146"/>
-      <c r="BG3" s="146"/>
-      <c r="BH3" s="146"/>
-      <c r="BI3" s="146"/>
-      <c r="BJ3" s="146"/>
-      <c r="BK3" s="146"/>
-      <c r="BL3" s="146"/>
-      <c r="BM3" s="146"/>
-      <c r="BN3" s="147"/>
-    </row>
-    <row r="4" spans="1:66" s="21" customFormat="1" ht="25.2" customHeight="1">
+      <c r="AJ3" s="150"/>
+      <c r="AK3" s="150"/>
+      <c r="AL3" s="150"/>
+      <c r="AM3" s="150"/>
+      <c r="AN3" s="150"/>
+      <c r="AO3" s="150"/>
+      <c r="AP3" s="150"/>
+      <c r="AQ3" s="150"/>
+      <c r="AR3" s="150"/>
+      <c r="AS3" s="150"/>
+      <c r="AT3" s="150"/>
+      <c r="AU3" s="150"/>
+      <c r="AV3" s="150"/>
+      <c r="AW3" s="150"/>
+      <c r="AX3" s="150"/>
+      <c r="AY3" s="150"/>
+      <c r="AZ3" s="150"/>
+      <c r="BA3" s="150"/>
+      <c r="BB3" s="150"/>
+      <c r="BC3" s="150"/>
+      <c r="BD3" s="150"/>
+      <c r="BE3" s="150"/>
+      <c r="BF3" s="150"/>
+      <c r="BG3" s="150"/>
+      <c r="BH3" s="150"/>
+      <c r="BI3" s="150"/>
+      <c r="BJ3" s="150"/>
+      <c r="BK3" s="150"/>
+      <c r="BL3" s="150"/>
+      <c r="BM3" s="150"/>
+      <c r="BN3" s="151"/>
+    </row>
+    <row r="4" spans="1:66" s="21" customFormat="1" ht="25.15" customHeight="1">
       <c r="A4" s="49"/>
       <c r="B4" s="53"/>
       <c r="C4" s="53"/>
@@ -13062,10 +13043,10 @@
       <c r="U4" s="60"/>
       <c r="V4" s="60"/>
       <c r="W4" s="60"/>
-      <c r="X4" s="152" t="s">
+      <c r="X4" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="Y4" s="153"/>
+      <c r="Y4" s="157"/>
       <c r="Z4" s="61" t="s">
         <v>61</v>
       </c>
@@ -13079,40 +13060,40 @@
       <c r="AF4" s="52"/>
       <c r="AG4" s="64"/>
       <c r="AH4" s="65"/>
-      <c r="AI4" s="148"/>
-      <c r="AJ4" s="149"/>
-      <c r="AK4" s="149"/>
-      <c r="AL4" s="149"/>
-      <c r="AM4" s="149"/>
-      <c r="AN4" s="149"/>
-      <c r="AO4" s="149"/>
-      <c r="AP4" s="149"/>
-      <c r="AQ4" s="149"/>
-      <c r="AR4" s="149"/>
-      <c r="AS4" s="149"/>
-      <c r="AT4" s="149"/>
-      <c r="AU4" s="149"/>
-      <c r="AV4" s="149"/>
-      <c r="AW4" s="149"/>
-      <c r="AX4" s="149"/>
-      <c r="AY4" s="149"/>
-      <c r="AZ4" s="149"/>
-      <c r="BA4" s="149"/>
-      <c r="BB4" s="149"/>
-      <c r="BC4" s="149"/>
-      <c r="BD4" s="149"/>
-      <c r="BE4" s="149"/>
-      <c r="BF4" s="149"/>
-      <c r="BG4" s="149"/>
-      <c r="BH4" s="149"/>
-      <c r="BI4" s="149"/>
-      <c r="BJ4" s="149"/>
-      <c r="BK4" s="149"/>
-      <c r="BL4" s="149"/>
-      <c r="BM4" s="149"/>
-      <c r="BN4" s="150"/>
-    </row>
-    <row r="5" spans="1:66" s="80" customFormat="1" ht="22.8">
+      <c r="AI4" s="152"/>
+      <c r="AJ4" s="153"/>
+      <c r="AK4" s="153"/>
+      <c r="AL4" s="153"/>
+      <c r="AM4" s="153"/>
+      <c r="AN4" s="153"/>
+      <c r="AO4" s="153"/>
+      <c r="AP4" s="153"/>
+      <c r="AQ4" s="153"/>
+      <c r="AR4" s="153"/>
+      <c r="AS4" s="153"/>
+      <c r="AT4" s="153"/>
+      <c r="AU4" s="153"/>
+      <c r="AV4" s="153"/>
+      <c r="AW4" s="153"/>
+      <c r="AX4" s="153"/>
+      <c r="AY4" s="153"/>
+      <c r="AZ4" s="153"/>
+      <c r="BA4" s="153"/>
+      <c r="BB4" s="153"/>
+      <c r="BC4" s="153"/>
+      <c r="BD4" s="153"/>
+      <c r="BE4" s="153"/>
+      <c r="BF4" s="153"/>
+      <c r="BG4" s="153"/>
+      <c r="BH4" s="153"/>
+      <c r="BI4" s="153"/>
+      <c r="BJ4" s="153"/>
+      <c r="BK4" s="153"/>
+      <c r="BL4" s="153"/>
+      <c r="BM4" s="153"/>
+      <c r="BN4" s="154"/>
+    </row>
+    <row r="5" spans="1:66" s="80" customFormat="1" ht="24">
       <c r="A5" s="66"/>
       <c r="B5" s="67" t="s">
         <v>62</v>
@@ -13236,7 +13217,7 @@
       <c r="BM5" s="79"/>
       <c r="BN5" s="79"/>
     </row>
-    <row r="6" spans="1:66" ht="19.2" customHeight="1">
+    <row r="6" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B6" s="81" t="s">
         <v>86</v>
       </c>
@@ -13246,16 +13227,16 @@
       <c r="D6" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="155">
+      <c r="E6" s="128">
         <v>0</v>
       </c>
-      <c r="F6" s="156">
+      <c r="F6" s="129">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G6" s="156">
+      <c r="G6" s="129">
         <v>0</v>
       </c>
-      <c r="H6" s="157" t="s">
+      <c r="H6" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I6" s="83" t="s">
@@ -13372,7 +13353,7 @@
       <c r="BM6" s="110"/>
       <c r="BN6" s="110"/>
     </row>
-    <row r="7" spans="1:66" ht="19.2" customHeight="1">
+    <row r="7" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B7" s="81" t="s">
         <v>88</v>
       </c>
@@ -13382,16 +13363,16 @@
       <c r="D7" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="155">
+      <c r="E7" s="128">
         <v>2.0649999999999999</v>
       </c>
-      <c r="F7" s="156">
+      <c r="F7" s="129">
         <v>0.04</v>
       </c>
-      <c r="G7" s="156">
+      <c r="G7" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H7" s="157" t="s">
+      <c r="H7" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I7" s="83" t="s">
@@ -13508,7 +13489,7 @@
       <c r="BM7" s="110"/>
       <c r="BN7" s="110"/>
     </row>
-    <row r="8" spans="1:66" ht="19.2" customHeight="1">
+    <row r="8" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B8" s="81" t="s">
         <v>88</v>
       </c>
@@ -13518,16 +13499,16 @@
       <c r="D8" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="155">
+      <c r="E8" s="128">
         <v>2.0649999999999999</v>
       </c>
-      <c r="F8" s="156">
+      <c r="F8" s="129">
         <v>0.04</v>
       </c>
-      <c r="G8" s="156">
+      <c r="G8" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H8" s="157" t="s">
+      <c r="H8" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I8" s="83" t="s">
@@ -13644,7 +13625,7 @@
       <c r="BM8" s="110"/>
       <c r="BN8" s="110"/>
     </row>
-    <row r="9" spans="1:66" ht="19.2" customHeight="1">
+    <row r="9" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B9" s="81" t="s">
         <v>88</v>
       </c>
@@ -13654,16 +13635,16 @@
       <c r="D9" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="155">
+      <c r="E9" s="128">
         <v>2.0649999999999999</v>
       </c>
-      <c r="F9" s="156">
+      <c r="F9" s="129">
         <v>0.04</v>
       </c>
-      <c r="G9" s="156">
+      <c r="G9" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H9" s="157" t="s">
+      <c r="H9" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="83" t="s">
@@ -13780,7 +13761,7 @@
       <c r="BM9" s="110"/>
       <c r="BN9" s="110"/>
     </row>
-    <row r="10" spans="1:66" ht="19.2" customHeight="1">
+    <row r="10" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B10" s="81" t="s">
         <v>88</v>
       </c>
@@ -13790,16 +13771,16 @@
       <c r="D10" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="155">
+      <c r="E10" s="128">
         <v>2.0649999999999999</v>
       </c>
-      <c r="F10" s="156">
+      <c r="F10" s="129">
         <v>0.04</v>
       </c>
-      <c r="G10" s="156">
+      <c r="G10" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H10" s="157" t="s">
+      <c r="H10" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I10" s="83" t="s">
@@ -13916,7 +13897,7 @@
       <c r="BM10" s="110"/>
       <c r="BN10" s="110"/>
     </row>
-    <row r="11" spans="1:66" ht="19.2" customHeight="1">
+    <row r="11" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B11" s="81" t="s">
         <v>89</v>
       </c>
@@ -13926,16 +13907,16 @@
       <c r="D11" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="155">
+      <c r="E11" s="128">
         <v>0.3</v>
       </c>
-      <c r="F11" s="156">
+      <c r="F11" s="129">
         <v>0.03</v>
       </c>
-      <c r="G11" s="156">
+      <c r="G11" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H11" s="157" t="s">
+      <c r="H11" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I11" s="83" t="s">
@@ -14052,7 +14033,7 @@
       <c r="BM11" s="110"/>
       <c r="BN11" s="110"/>
     </row>
-    <row r="12" spans="1:66" ht="19.2" customHeight="1">
+    <row r="12" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B12" s="81" t="s">
         <v>89</v>
       </c>
@@ -14062,16 +14043,16 @@
       <c r="D12" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="155">
+      <c r="E12" s="128">
         <v>0.3</v>
       </c>
-      <c r="F12" s="156">
+      <c r="F12" s="129">
         <v>0.03</v>
       </c>
-      <c r="G12" s="156">
+      <c r="G12" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H12" s="157" t="s">
+      <c r="H12" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I12" s="83" t="s">
@@ -14188,7 +14169,7 @@
       <c r="BM12" s="110"/>
       <c r="BN12" s="110"/>
     </row>
-    <row r="13" spans="1:66" ht="19.2" customHeight="1">
+    <row r="13" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B13" s="81" t="s">
         <v>90</v>
       </c>
@@ -14198,16 +14179,16 @@
       <c r="D13" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="155">
+      <c r="E13" s="128">
         <v>0.32</v>
       </c>
-      <c r="F13" s="156">
+      <c r="F13" s="129">
         <v>0.03</v>
       </c>
-      <c r="G13" s="156">
+      <c r="G13" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H13" s="157" t="s">
+      <c r="H13" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I13" s="83" t="s">
@@ -14324,7 +14305,7 @@
       <c r="BM13" s="110"/>
       <c r="BN13" s="110"/>
     </row>
-    <row r="14" spans="1:66" ht="19.2" customHeight="1">
+    <row r="14" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B14" s="81" t="s">
         <v>90</v>
       </c>
@@ -14334,16 +14315,16 @@
       <c r="D14" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="155">
+      <c r="E14" s="128">
         <v>0.32</v>
       </c>
-      <c r="F14" s="156">
+      <c r="F14" s="129">
         <v>0.03</v>
       </c>
-      <c r="G14" s="156">
+      <c r="G14" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H14" s="157" t="s">
+      <c r="H14" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I14" s="83" t="s">
@@ -14460,7 +14441,7 @@
       <c r="BM14" s="110"/>
       <c r="BN14" s="110"/>
     </row>
-    <row r="15" spans="1:66" ht="19.2" customHeight="1">
+    <row r="15" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B15" s="81" t="s">
         <v>91</v>
       </c>
@@ -14470,16 +14451,16 @@
       <c r="D15" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="155">
+      <c r="E15" s="128">
         <v>0.1</v>
       </c>
-      <c r="F15" s="156">
+      <c r="F15" s="129">
         <v>0.01</v>
       </c>
-      <c r="G15" s="156">
+      <c r="G15" s="129">
         <v>-0.04</v>
       </c>
-      <c r="H15" s="157" t="s">
+      <c r="H15" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I15" s="83" t="s">
@@ -14596,7 +14577,7 @@
       <c r="BM15" s="110"/>
       <c r="BN15" s="110"/>
     </row>
-    <row r="16" spans="1:66" ht="19.2" customHeight="1">
+    <row r="16" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B16" s="81" t="s">
         <v>91</v>
       </c>
@@ -14606,16 +14587,16 @@
       <c r="D16" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="155">
+      <c r="E16" s="128">
         <v>0.1</v>
       </c>
-      <c r="F16" s="156">
+      <c r="F16" s="129">
         <v>0.01</v>
       </c>
-      <c r="G16" s="156">
+      <c r="G16" s="129">
         <v>-0.04</v>
       </c>
-      <c r="H16" s="157" t="s">
+      <c r="H16" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I16" s="83" t="s">
@@ -14732,7 +14713,7 @@
       <c r="BM16" s="110"/>
       <c r="BN16" s="110"/>
     </row>
-    <row r="17" spans="2:66" ht="19.2" customHeight="1">
+    <row r="17" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B17" s="81" t="s">
         <v>91</v>
       </c>
@@ -14742,16 +14723,16 @@
       <c r="D17" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="155">
+      <c r="E17" s="128">
         <v>0.1</v>
       </c>
-      <c r="F17" s="156">
+      <c r="F17" s="129">
         <v>0.01</v>
       </c>
-      <c r="G17" s="156">
+      <c r="G17" s="129">
         <v>-0.04</v>
       </c>
-      <c r="H17" s="157" t="s">
+      <c r="H17" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I17" s="83" t="s">
@@ -14868,7 +14849,7 @@
       <c r="BM17" s="110"/>
       <c r="BN17" s="110"/>
     </row>
-    <row r="18" spans="2:66" ht="19.2" customHeight="1">
+    <row r="18" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B18" s="81" t="s">
         <v>91</v>
       </c>
@@ -14878,16 +14859,16 @@
       <c r="D18" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="155">
+      <c r="E18" s="128">
         <v>0.1</v>
       </c>
-      <c r="F18" s="156">
+      <c r="F18" s="129">
         <v>0.01</v>
       </c>
-      <c r="G18" s="156">
+      <c r="G18" s="129">
         <v>-0.04</v>
       </c>
-      <c r="H18" s="157" t="s">
+      <c r="H18" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I18" s="83" t="s">
@@ -15004,7 +14985,7 @@
       <c r="BM18" s="110"/>
       <c r="BN18" s="110"/>
     </row>
-    <row r="19" spans="2:66" ht="19.2" customHeight="1">
+    <row r="19" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B19" s="81" t="s">
         <v>92</v>
       </c>
@@ -15014,16 +14995,16 @@
       <c r="D19" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="155">
+      <c r="E19" s="128">
         <v>90</v>
       </c>
-      <c r="F19" s="156">
+      <c r="F19" s="129">
         <v>1</v>
       </c>
-      <c r="G19" s="156">
+      <c r="G19" s="129">
         <v>-2</v>
       </c>
-      <c r="H19" s="157" t="s">
+      <c r="H19" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I19" s="83" t="s">
@@ -15140,7 +15121,7 @@
       <c r="BM19" s="110"/>
       <c r="BN19" s="110"/>
     </row>
-    <row r="20" spans="2:66" ht="19.2" customHeight="1">
+    <row r="20" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B20" s="81" t="s">
         <v>92</v>
       </c>
@@ -15150,16 +15131,16 @@
       <c r="D20" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="155">
+      <c r="E20" s="128">
         <v>90</v>
       </c>
-      <c r="F20" s="156">
+      <c r="F20" s="129">
         <v>1</v>
       </c>
-      <c r="G20" s="156">
+      <c r="G20" s="129">
         <v>-2</v>
       </c>
-      <c r="H20" s="157" t="s">
+      <c r="H20" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I20" s="83" t="s">
@@ -15276,7 +15257,7 @@
       <c r="BM20" s="110"/>
       <c r="BN20" s="110"/>
     </row>
-    <row r="21" spans="2:66" ht="19.2" customHeight="1">
+    <row r="21" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B21" s="81" t="s">
         <v>93</v>
       </c>
@@ -15286,16 +15267,16 @@
       <c r="D21" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="155">
+      <c r="E21" s="128">
         <v>90</v>
       </c>
-      <c r="F21" s="156">
+      <c r="F21" s="129">
         <v>1</v>
       </c>
-      <c r="G21" s="156">
+      <c r="G21" s="129">
         <v>-2</v>
       </c>
-      <c r="H21" s="157" t="s">
+      <c r="H21" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I21" s="83" t="s">
@@ -15412,7 +15393,7 @@
       <c r="BM21" s="110"/>
       <c r="BN21" s="110"/>
     </row>
-    <row r="22" spans="2:66" ht="19.2" customHeight="1">
+    <row r="22" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B22" s="81" t="s">
         <v>93</v>
       </c>
@@ -15422,16 +15403,16 @@
       <c r="D22" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="155">
+      <c r="E22" s="128">
         <v>90</v>
       </c>
-      <c r="F22" s="156">
+      <c r="F22" s="129">
         <v>1</v>
       </c>
-      <c r="G22" s="156">
+      <c r="G22" s="129">
         <v>-2</v>
       </c>
-      <c r="H22" s="157" t="s">
+      <c r="H22" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I22" s="83" t="s">
@@ -15548,7 +15529,7 @@
       <c r="BM22" s="110"/>
       <c r="BN22" s="110"/>
     </row>
-    <row r="23" spans="2:66" ht="19.2" customHeight="1">
+    <row r="23" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B23" s="81" t="s">
         <v>94</v>
       </c>
@@ -15558,16 +15539,16 @@
       <c r="D23" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="155">
+      <c r="E23" s="128">
         <v>0.122</v>
       </c>
-      <c r="F23" s="156">
+      <c r="F23" s="129">
         <v>0.01</v>
       </c>
-      <c r="G23" s="156">
+      <c r="G23" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H23" s="157" t="s">
+      <c r="H23" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I23" s="83" t="s">
@@ -15684,7 +15665,7 @@
       <c r="BM23" s="110"/>
       <c r="BN23" s="110"/>
     </row>
-    <row r="24" spans="2:66" ht="19.2" customHeight="1">
+    <row r="24" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B24" s="81" t="s">
         <v>95</v>
       </c>
@@ -15694,16 +15675,16 @@
       <c r="D24" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="155">
+      <c r="E24" s="128">
         <v>0.122</v>
       </c>
-      <c r="F24" s="156">
+      <c r="F24" s="129">
         <v>0.01</v>
       </c>
-      <c r="G24" s="156">
+      <c r="G24" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H24" s="157" t="s">
+      <c r="H24" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I24" s="83" t="s">
@@ -15820,7 +15801,7 @@
       <c r="BM24" s="110"/>
       <c r="BN24" s="110"/>
     </row>
-    <row r="25" spans="2:66" ht="19.2" customHeight="1">
+    <row r="25" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B25" s="81" t="s">
         <v>101</v>
       </c>
@@ -15830,16 +15811,16 @@
       <c r="D25" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="155">
+      <c r="E25" s="128">
         <v>7.8E-2</v>
       </c>
-      <c r="F25" s="156">
+      <c r="F25" s="129">
         <v>0.01</v>
       </c>
-      <c r="G25" s="156">
+      <c r="G25" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H25" s="157" t="s">
+      <c r="H25" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I25" s="83" t="s">
@@ -15944,7 +15925,7 @@
       <c r="BM25" s="110"/>
       <c r="BN25" s="110"/>
     </row>
-    <row r="26" spans="2:66" ht="19.2" customHeight="1">
+    <row r="26" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B26" s="81" t="s">
         <v>102</v>
       </c>
@@ -15954,16 +15935,16 @@
       <c r="D26" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="155">
+      <c r="E26" s="128">
         <v>7.8E-2</v>
       </c>
-      <c r="F26" s="156">
+      <c r="F26" s="129">
         <v>0.01</v>
       </c>
-      <c r="G26" s="156">
+      <c r="G26" s="129">
         <v>-0.02</v>
       </c>
-      <c r="H26" s="157" t="s">
+      <c r="H26" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I26" s="83" t="s">
@@ -16068,7 +16049,7 @@
       <c r="BM26" s="110"/>
       <c r="BN26" s="110"/>
     </row>
-    <row r="27" spans="2:66" ht="19.2" customHeight="1">
+    <row r="27" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B27" s="81" t="s">
         <v>106</v>
       </c>
@@ -16078,16 +16059,16 @@
       <c r="D27" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="155">
+      <c r="E27" s="128">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F27" s="156">
+      <c r="F27" s="129">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G27" s="156">
+      <c r="G27" s="129">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H27" s="157" t="s">
+      <c r="H27" s="130" t="s">
         <v>99</v>
       </c>
       <c r="I27" s="83" t="s">
@@ -16192,7 +16173,7 @@
       <c r="BM27" s="110"/>
       <c r="BN27" s="110"/>
     </row>
-    <row r="28" spans="2:66" ht="19.2" customHeight="1">
+    <row r="28" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B28" s="81" t="s">
         <v>103</v>
       </c>
@@ -16202,16 +16183,16 @@
       <c r="D28" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="155">
+      <c r="E28" s="128">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F28" s="156">
+      <c r="F28" s="129">
         <v>0.03</v>
       </c>
-      <c r="G28" s="156">
+      <c r="G28" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H28" s="157" t="s">
+      <c r="H28" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I28" s="83" t="s">
@@ -16316,7 +16297,7 @@
       <c r="BM28" s="110"/>
       <c r="BN28" s="110"/>
     </row>
-    <row r="29" spans="2:66" ht="19.2" customHeight="1">
+    <row r="29" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B29" s="81" t="s">
         <v>103</v>
       </c>
@@ -16326,16 +16307,16 @@
       <c r="D29" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="155">
+      <c r="E29" s="128">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F29" s="156">
+      <c r="F29" s="129">
         <v>0.03</v>
       </c>
-      <c r="G29" s="156">
+      <c r="G29" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H29" s="157" t="s">
+      <c r="H29" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I29" s="83" t="s">
@@ -16440,7 +16421,7 @@
       <c r="BM29" s="110"/>
       <c r="BN29" s="110"/>
     </row>
-    <row r="30" spans="2:66" ht="19.2" customHeight="1">
+    <row r="30" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B30" s="81" t="s">
         <v>104</v>
       </c>
@@ -16450,16 +16431,16 @@
       <c r="D30" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="155">
+      <c r="E30" s="128">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F30" s="156">
+      <c r="F30" s="129">
         <v>0.03</v>
       </c>
-      <c r="G30" s="156">
+      <c r="G30" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H30" s="157" t="s">
+      <c r="H30" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I30" s="83" t="s">
@@ -16576,7 +16557,7 @@
       <c r="BM30" s="110"/>
       <c r="BN30" s="110"/>
     </row>
-    <row r="31" spans="2:66" ht="19.2" customHeight="1">
+    <row r="31" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B31" s="81" t="s">
         <v>104</v>
       </c>
@@ -16586,16 +16567,16 @@
       <c r="D31" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="155">
+      <c r="E31" s="128">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F31" s="156">
+      <c r="F31" s="129">
         <v>0.03</v>
       </c>
-      <c r="G31" s="156">
+      <c r="G31" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H31" s="157" t="s">
+      <c r="H31" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I31" s="83" t="s">
@@ -16712,7 +16693,7 @@
       <c r="BM31" s="110"/>
       <c r="BN31" s="110"/>
     </row>
-    <row r="32" spans="2:66" ht="19.2" customHeight="1">
+    <row r="32" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B32" s="81" t="s">
         <v>105</v>
       </c>
@@ -16722,16 +16703,16 @@
       <c r="D32" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="155">
+      <c r="E32" s="128">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F32" s="156">
+      <c r="F32" s="129">
         <v>0.03</v>
       </c>
-      <c r="G32" s="156">
+      <c r="G32" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H32" s="157" t="s">
+      <c r="H32" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I32" s="83" t="s">
@@ -16848,7 +16829,7 @@
       <c r="BM32" s="110"/>
       <c r="BN32" s="110"/>
     </row>
-    <row r="33" spans="2:66" ht="19.2" customHeight="1">
+    <row r="33" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B33" s="81" t="s">
         <v>105</v>
       </c>
@@ -16858,16 +16839,16 @@
       <c r="D33" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="155">
+      <c r="E33" s="128">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F33" s="156">
+      <c r="F33" s="129">
         <v>0.03</v>
       </c>
-      <c r="G33" s="156">
+      <c r="G33" s="129">
         <v>-0.03</v>
       </c>
-      <c r="H33" s="157" t="s">
+      <c r="H33" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I33" s="83" t="s">
@@ -16984,7 +16965,7 @@
       <c r="BM33" s="110"/>
       <c r="BN33" s="110"/>
     </row>
-    <row r="34" spans="2:66" ht="19.2" customHeight="1">
+    <row r="34" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B34" s="81" t="s">
         <v>96</v>
       </c>
@@ -16994,16 +16975,16 @@
       <c r="D34" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="155">
+      <c r="E34" s="128">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F34" s="156">
+      <c r="F34" s="129">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G34" s="156">
+      <c r="G34" s="129">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H34" s="157" t="s">
+      <c r="H34" s="130" t="s">
         <v>99</v>
       </c>
       <c r="I34" s="83" t="s">
@@ -17120,7 +17101,7 @@
       <c r="BM34" s="110"/>
       <c r="BN34" s="110"/>
     </row>
-    <row r="35" spans="2:66" ht="19.2" customHeight="1">
+    <row r="35" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B35" s="81" t="s">
         <v>96</v>
       </c>
@@ -17130,16 +17111,16 @@
       <c r="D35" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="155">
+      <c r="E35" s="128">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F35" s="156">
+      <c r="F35" s="129">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G35" s="156">
+      <c r="G35" s="129">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H35" s="157" t="s">
+      <c r="H35" s="130" t="s">
         <v>99</v>
       </c>
       <c r="I35" s="83" t="s">
@@ -17256,7 +17237,7 @@
       <c r="BM35" s="110"/>
       <c r="BN35" s="110"/>
     </row>
-    <row r="36" spans="2:66" ht="19.2" customHeight="1">
+    <row r="36" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B36" s="81" t="s">
         <v>97</v>
       </c>
@@ -17266,16 +17247,16 @@
       <c r="D36" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="155">
+      <c r="E36" s="128">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F36" s="156">
+      <c r="F36" s="129">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G36" s="156">
+      <c r="G36" s="129">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H36" s="157" t="s">
+      <c r="H36" s="130" t="s">
         <v>99</v>
       </c>
       <c r="I36" s="83" t="s">
@@ -17392,7 +17373,7 @@
       <c r="BM36" s="110"/>
       <c r="BN36" s="110"/>
     </row>
-    <row r="37" spans="2:66" ht="19.2" customHeight="1">
+    <row r="37" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B37" s="94" t="s">
         <v>97</v>
       </c>
@@ -17402,16 +17383,16 @@
       <c r="D37" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="155">
+      <c r="E37" s="128">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F37" s="156">
+      <c r="F37" s="129">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G37" s="156">
+      <c r="G37" s="129">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H37" s="157" t="s">
+      <c r="H37" s="130" t="s">
         <v>99</v>
       </c>
       <c r="I37" s="83" t="s">
@@ -17528,7 +17509,7 @@
       <c r="BM37" s="110"/>
       <c r="BN37" s="110"/>
     </row>
-    <row r="38" spans="2:66" ht="19.2" customHeight="1">
+    <row r="38" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B38" s="96"/>
       <c r="C38" s="21"/>
       <c r="D38" s="97"/>
@@ -17594,7 +17575,7 @@
       <c r="BM38" s="108"/>
       <c r="BN38" s="108"/>
     </row>
-    <row r="39" spans="2:66" ht="19.2" customHeight="1">
+    <row r="39" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B39" s="96"/>
       <c r="C39" s="21"/>
       <c r="D39" s="97"/>
@@ -17660,7 +17641,7 @@
       <c r="BM39" s="108"/>
       <c r="BN39" s="108"/>
     </row>
-    <row r="40" spans="2:66" ht="19.2" customHeight="1">
+    <row r="40" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B40" s="96"/>
       <c r="C40" s="21"/>
       <c r="D40" s="97"/>
@@ -17726,7 +17707,7 @@
       <c r="BM40" s="108"/>
       <c r="BN40" s="108"/>
     </row>
-    <row r="41" spans="2:66" ht="19.2" customHeight="1">
+    <row r="41" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B41" s="96"/>
       <c r="C41" s="21"/>
       <c r="D41" s="97"/>
@@ -17792,7 +17773,7 @@
       <c r="BM41" s="108"/>
       <c r="BN41" s="108"/>
     </row>
-    <row r="42" spans="2:66" ht="19.2" customHeight="1">
+    <row r="42" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B42" s="96"/>
       <c r="C42" s="21"/>
       <c r="D42" s="97"/>
@@ -17858,7 +17839,7 @@
       <c r="BM42" s="108"/>
       <c r="BN42" s="108"/>
     </row>
-    <row r="43" spans="2:66" ht="19.2" customHeight="1">
+    <row r="43" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B43" s="96"/>
       <c r="C43" s="21"/>
       <c r="D43" s="97"/>
@@ -17924,7 +17905,7 @@
       <c r="BM43" s="108"/>
       <c r="BN43" s="108"/>
     </row>
-    <row r="44" spans="2:66" ht="19.2" customHeight="1">
+    <row r="44" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B44" s="96"/>
       <c r="C44" s="21"/>
       <c r="D44" s="97"/>
@@ -17990,7 +17971,7 @@
       <c r="BM44" s="108"/>
       <c r="BN44" s="108"/>
     </row>
-    <row r="45" spans="2:66" ht="19.2" customHeight="1">
+    <row r="45" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B45" s="96"/>
       <c r="C45" s="21"/>
       <c r="D45" s="97"/>
@@ -18056,7 +18037,7 @@
       <c r="BM45" s="108"/>
       <c r="BN45" s="108"/>
     </row>
-    <row r="46" spans="2:66" ht="19.2" customHeight="1">
+    <row r="46" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B46" s="96"/>
       <c r="C46" s="21"/>
       <c r="D46" s="97"/>
@@ -18122,7 +18103,7 @@
       <c r="BM46" s="108"/>
       <c r="BN46" s="108"/>
     </row>
-    <row r="47" spans="2:66" ht="19.2" customHeight="1">
+    <row r="47" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B47" s="96"/>
       <c r="C47" s="21"/>
       <c r="D47" s="97"/>
@@ -18188,7 +18169,7 @@
       <c r="BM47" s="108"/>
       <c r="BN47" s="108"/>
     </row>
-    <row r="48" spans="2:66" ht="19.2" customHeight="1">
+    <row r="48" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B48" s="96"/>
       <c r="C48" s="21"/>
       <c r="D48" s="97"/>
@@ -18254,7 +18235,7 @@
       <c r="BM48" s="108"/>
       <c r="BN48" s="108"/>
     </row>
-    <row r="49" spans="2:66" ht="19.2" customHeight="1">
+    <row r="49" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B49" s="96"/>
       <c r="C49" s="21"/>
       <c r="D49" s="97"/>
@@ -18320,7 +18301,7 @@
       <c r="BM49" s="108"/>
       <c r="BN49" s="108"/>
     </row>
-    <row r="50" spans="2:66" ht="19.2" customHeight="1">
+    <row r="50" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B50" s="96"/>
       <c r="C50" s="21"/>
       <c r="D50" s="97"/>
@@ -18386,7 +18367,7 @@
       <c r="BM50" s="108"/>
       <c r="BN50" s="108"/>
     </row>
-    <row r="51" spans="2:66" ht="19.2" customHeight="1">
+    <row r="51" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B51" s="96"/>
       <c r="C51" s="21"/>
       <c r="D51" s="97"/>
@@ -18452,7 +18433,7 @@
       <c r="BM51" s="108"/>
       <c r="BN51" s="108"/>
     </row>
-    <row r="52" spans="2:66" ht="19.2" customHeight="1">
+    <row r="52" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B52" s="96"/>
       <c r="C52" s="21"/>
       <c r="D52" s="97"/>
@@ -18518,7 +18499,7 @@
       <c r="BM52" s="108"/>
       <c r="BN52" s="108"/>
     </row>
-    <row r="53" spans="2:66" ht="19.2" customHeight="1">
+    <row r="53" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B53" s="96"/>
       <c r="C53" s="21"/>
       <c r="D53" s="97"/>
@@ -18584,7 +18565,7 @@
       <c r="BM53" s="108"/>
       <c r="BN53" s="108"/>
     </row>
-    <row r="54" spans="2:66" ht="19.2" customHeight="1">
+    <row r="54" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B54" s="96"/>
       <c r="C54" s="21"/>
       <c r="D54" s="97"/>
@@ -18650,7 +18631,7 @@
       <c r="BM54" s="108"/>
       <c r="BN54" s="108"/>
     </row>
-    <row r="55" spans="2:66" ht="19.2" customHeight="1">
+    <row r="55" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B55" s="96"/>
       <c r="C55" s="21"/>
       <c r="D55" s="97"/>
@@ -18716,7 +18697,7 @@
       <c r="BM55" s="108"/>
       <c r="BN55" s="108"/>
     </row>
-    <row r="56" spans="2:66" ht="19.2" customHeight="1">
+    <row r="56" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B56" s="96"/>
       <c r="C56" s="21"/>
       <c r="D56" s="97"/>
@@ -18782,7 +18763,7 @@
       <c r="BM56" s="108"/>
       <c r="BN56" s="108"/>
     </row>
-    <row r="57" spans="2:66" ht="19.2" customHeight="1">
+    <row r="57" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B57" s="96"/>
       <c r="C57" s="21"/>
       <c r="D57" s="97"/>
@@ -18848,7 +18829,7 @@
       <c r="BM57" s="108"/>
       <c r="BN57" s="108"/>
     </row>
-    <row r="58" spans="2:66" ht="19.2" customHeight="1">
+    <row r="58" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B58" s="96"/>
       <c r="C58" s="21"/>
       <c r="D58" s="97"/>
@@ -18914,7 +18895,7 @@
       <c r="BM58" s="108"/>
       <c r="BN58" s="108"/>
     </row>
-    <row r="59" spans="2:66" ht="19.2" customHeight="1">
+    <row r="59" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B59" s="96"/>
       <c r="C59" s="21"/>
       <c r="D59" s="97"/>
@@ -18980,7 +18961,7 @@
       <c r="BM59" s="108"/>
       <c r="BN59" s="108"/>
     </row>
-    <row r="60" spans="2:66" ht="19.2" customHeight="1">
+    <row r="60" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B60" s="96"/>
       <c r="C60" s="21"/>
       <c r="D60" s="97"/>
@@ -19046,7 +19027,7 @@
       <c r="BM60" s="108"/>
       <c r="BN60" s="108"/>
     </row>
-    <row r="61" spans="2:66" ht="19.2" customHeight="1">
+    <row r="61" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B61" s="96"/>
       <c r="C61" s="21"/>
       <c r="D61" s="97"/>
@@ -19112,7 +19093,7 @@
       <c r="BM61" s="108"/>
       <c r="BN61" s="108"/>
     </row>
-    <row r="62" spans="2:66" ht="19.2" customHeight="1">
+    <row r="62" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B62" s="96"/>
       <c r="C62" s="21"/>
       <c r="D62" s="97"/>
@@ -19178,7 +19159,7 @@
       <c r="BM62" s="108"/>
       <c r="BN62" s="108"/>
     </row>
-    <row r="63" spans="2:66" ht="19.2" customHeight="1">
+    <row r="63" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B63" s="96"/>
       <c r="C63" s="21"/>
       <c r="D63" s="97"/>
@@ -19244,7 +19225,7 @@
       <c r="BM63" s="108"/>
       <c r="BN63" s="108"/>
     </row>
-    <row r="64" spans="2:66" ht="19.2" customHeight="1">
+    <row r="64" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B64" s="96"/>
       <c r="C64" s="21"/>
       <c r="D64" s="97"/>
@@ -19310,7 +19291,7 @@
       <c r="BM64" s="108"/>
       <c r="BN64" s="108"/>
     </row>
-    <row r="65" spans="2:66" ht="19.2" customHeight="1">
+    <row r="65" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B65" s="96"/>
       <c r="C65" s="21"/>
       <c r="D65" s="97"/>
@@ -19376,7 +19357,7 @@
       <c r="BM65" s="108"/>
       <c r="BN65" s="108"/>
     </row>
-    <row r="66" spans="2:66" ht="19.2" customHeight="1">
+    <row r="66" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B66" s="96"/>
       <c r="C66" s="21"/>
       <c r="D66" s="97"/>
@@ -19442,7 +19423,7 @@
       <c r="BM66" s="108"/>
       <c r="BN66" s="108"/>
     </row>
-    <row r="67" spans="2:66" ht="19.2" customHeight="1">
+    <row r="67" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B67" s="96"/>
       <c r="C67" s="21"/>
       <c r="D67" s="97"/>
@@ -19508,7 +19489,7 @@
       <c r="BM67" s="108"/>
       <c r="BN67" s="108"/>
     </row>
-    <row r="68" spans="2:66" ht="19.2" customHeight="1">
+    <row r="68" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B68" s="96"/>
       <c r="C68" s="21"/>
       <c r="D68" s="97"/>
@@ -19574,7 +19555,7 @@
       <c r="BM68" s="108"/>
       <c r="BN68" s="108"/>
     </row>
-    <row r="69" spans="2:66" ht="19.2" customHeight="1">
+    <row r="69" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B69" s="96"/>
       <c r="C69" s="21"/>
       <c r="D69" s="97"/>
@@ -19640,7 +19621,7 @@
       <c r="BM69" s="108"/>
       <c r="BN69" s="108"/>
     </row>
-    <row r="70" spans="2:66" ht="19.2" customHeight="1">
+    <row r="70" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B70" s="96"/>
       <c r="C70" s="21"/>
       <c r="D70" s="97"/>
@@ -19706,7 +19687,7 @@
       <c r="BM70" s="108"/>
       <c r="BN70" s="108"/>
     </row>
-    <row r="71" spans="2:66" ht="19.2" customHeight="1">
+    <row r="71" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B71" s="96"/>
       <c r="C71" s="21"/>
       <c r="D71" s="97"/>
@@ -19772,7 +19753,7 @@
       <c r="BM71" s="108"/>
       <c r="BN71" s="108"/>
     </row>
-    <row r="72" spans="2:66" ht="19.2" customHeight="1">
+    <row r="72" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B72" s="96"/>
       <c r="C72" s="21"/>
       <c r="D72" s="97"/>
@@ -19838,7 +19819,7 @@
       <c r="BM72" s="108"/>
       <c r="BN72" s="108"/>
     </row>
-    <row r="73" spans="2:66" ht="19.2" customHeight="1">
+    <row r="73" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B73" s="96"/>
       <c r="C73" s="21"/>
       <c r="D73" s="97"/>
@@ -19904,7 +19885,7 @@
       <c r="BM73" s="108"/>
       <c r="BN73" s="108"/>
     </row>
-    <row r="74" spans="2:66" ht="19.2" customHeight="1">
+    <row r="74" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B74" s="96"/>
       <c r="C74" s="21"/>
       <c r="D74" s="97"/>
@@ -19970,7 +19951,7 @@
       <c r="BM74" s="108"/>
       <c r="BN74" s="108"/>
     </row>
-    <row r="75" spans="2:66" ht="19.2" customHeight="1">
+    <row r="75" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B75" s="96"/>
       <c r="C75" s="21"/>
       <c r="D75" s="97"/>
@@ -20036,7 +20017,7 @@
       <c r="BM75" s="108"/>
       <c r="BN75" s="108"/>
     </row>
-    <row r="76" spans="2:66" ht="19.2" customHeight="1">
+    <row r="76" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B76" s="96"/>
       <c r="C76" s="21"/>
       <c r="D76" s="97"/>
@@ -20102,7 +20083,7 @@
       <c r="BM76" s="108"/>
       <c r="BN76" s="108"/>
     </row>
-    <row r="77" spans="2:66" ht="19.2" customHeight="1">
+    <row r="77" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B77" s="96"/>
       <c r="C77" s="21"/>
       <c r="D77" s="97"/>
@@ -20168,7 +20149,7 @@
       <c r="BM77" s="108"/>
       <c r="BN77" s="108"/>
     </row>
-    <row r="78" spans="2:66" ht="19.2" customHeight="1">
+    <row r="78" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B78" s="96"/>
       <c r="C78" s="21"/>
       <c r="D78" s="97"/>
@@ -20234,7 +20215,7 @@
       <c r="BM78" s="108"/>
       <c r="BN78" s="108"/>
     </row>
-    <row r="79" spans="2:66" ht="19.2" customHeight="1">
+    <row r="79" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B79" s="96"/>
       <c r="C79" s="21"/>
       <c r="D79" s="97"/>
@@ -20300,7 +20281,7 @@
       <c r="BM79" s="108"/>
       <c r="BN79" s="108"/>
     </row>
-    <row r="80" spans="2:66" ht="19.2" customHeight="1">
+    <row r="80" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B80" s="96"/>
       <c r="C80" s="21"/>
       <c r="D80" s="97"/>
@@ -20366,7 +20347,7 @@
       <c r="BM80" s="108"/>
       <c r="BN80" s="108"/>
     </row>
-    <row r="81" spans="2:66" ht="19.2" customHeight="1">
+    <row r="81" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B81" s="96"/>
       <c r="C81" s="21"/>
       <c r="D81" s="97"/>
@@ -20432,7 +20413,7 @@
       <c r="BM81" s="108"/>
       <c r="BN81" s="108"/>
     </row>
-    <row r="82" spans="2:66" ht="19.2" customHeight="1">
+    <row r="82" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B82" s="96"/>
       <c r="C82" s="21"/>
       <c r="D82" s="97"/>
@@ -20498,7 +20479,7 @@
       <c r="BM82" s="108"/>
       <c r="BN82" s="108"/>
     </row>
-    <row r="83" spans="2:66" ht="19.2" customHeight="1">
+    <row r="83" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B83" s="96"/>
       <c r="C83" s="21"/>
       <c r="D83" s="97"/>
@@ -20564,7 +20545,7 @@
       <c r="BM83" s="108"/>
       <c r="BN83" s="108"/>
     </row>
-    <row r="84" spans="2:66" ht="19.2" customHeight="1">
+    <row r="84" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B84" s="96"/>
       <c r="C84" s="21"/>
       <c r="D84" s="97"/>
@@ -20630,7 +20611,7 @@
       <c r="BM84" s="108"/>
       <c r="BN84" s="108"/>
     </row>
-    <row r="85" spans="2:66" ht="19.2" customHeight="1">
+    <row r="85" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B85" s="96"/>
       <c r="C85" s="21"/>
       <c r="D85" s="97"/>
@@ -20696,7 +20677,7 @@
       <c r="BM85" s="108"/>
       <c r="BN85" s="108"/>
     </row>
-    <row r="86" spans="2:66" ht="19.2" customHeight="1">
+    <row r="86" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B86" s="96"/>
       <c r="C86" s="21"/>
       <c r="D86" s="97"/>
@@ -20762,7 +20743,7 @@
       <c r="BM86" s="108"/>
       <c r="BN86" s="108"/>
     </row>
-    <row r="87" spans="2:66" ht="19.2" customHeight="1">
+    <row r="87" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B87" s="96"/>
       <c r="C87" s="21"/>
       <c r="D87" s="97"/>
@@ -20828,7 +20809,7 @@
       <c r="BM87" s="108"/>
       <c r="BN87" s="108"/>
     </row>
-    <row r="88" spans="2:66" ht="19.2" customHeight="1">
+    <row r="88" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B88" s="96"/>
       <c r="C88" s="21"/>
       <c r="D88" s="97"/>
@@ -20894,7 +20875,7 @@
       <c r="BM88" s="108"/>
       <c r="BN88" s="108"/>
     </row>
-    <row r="89" spans="2:66" ht="19.2" customHeight="1">
+    <row r="89" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B89" s="96"/>
       <c r="C89" s="21"/>
       <c r="D89" s="97"/>
@@ -20960,7 +20941,7 @@
       <c r="BM89" s="108"/>
       <c r="BN89" s="108"/>
     </row>
-    <row r="90" spans="2:66" ht="19.2" customHeight="1">
+    <row r="90" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B90" s="96"/>
       <c r="C90" s="21"/>
       <c r="D90" s="97"/>
@@ -21026,7 +21007,7 @@
       <c r="BM90" s="108"/>
       <c r="BN90" s="108"/>
     </row>
-    <row r="91" spans="2:66" ht="19.2" customHeight="1">
+    <row r="91" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B91" s="96"/>
       <c r="C91" s="21"/>
       <c r="D91" s="97"/>
@@ -21092,7 +21073,7 @@
       <c r="BM91" s="108"/>
       <c r="BN91" s="108"/>
     </row>
-    <row r="92" spans="2:66" ht="19.2" customHeight="1">
+    <row r="92" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B92" s="96"/>
       <c r="C92" s="21"/>
       <c r="D92" s="97"/>
@@ -21158,7 +21139,7 @@
       <c r="BM92" s="108"/>
       <c r="BN92" s="108"/>
     </row>
-    <row r="93" spans="2:66" ht="19.2" customHeight="1">
+    <row r="93" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B93" s="96"/>
       <c r="C93" s="21"/>
       <c r="D93" s="97"/>
@@ -21224,7 +21205,7 @@
       <c r="BM93" s="108"/>
       <c r="BN93" s="108"/>
     </row>
-    <row r="94" spans="2:66" ht="19.2" customHeight="1">
+    <row r="94" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B94" s="96"/>
       <c r="C94" s="21"/>
       <c r="D94" s="97"/>
@@ -21290,7 +21271,7 @@
       <c r="BM94" s="108"/>
       <c r="BN94" s="108"/>
     </row>
-    <row r="95" spans="2:66" ht="19.2" customHeight="1">
+    <row r="95" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B95" s="96"/>
       <c r="C95" s="21"/>
       <c r="D95" s="97"/>
@@ -21356,7 +21337,7 @@
       <c r="BM95" s="108"/>
       <c r="BN95" s="108"/>
     </row>
-    <row r="96" spans="2:66" ht="19.2" customHeight="1">
+    <row r="96" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B96" s="96"/>
       <c r="C96" s="21"/>
       <c r="D96" s="97"/>
@@ -21422,7 +21403,7 @@
       <c r="BM96" s="108"/>
       <c r="BN96" s="108"/>
     </row>
-    <row r="97" spans="2:66" ht="19.2" customHeight="1">
+    <row r="97" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B97" s="96"/>
       <c r="C97" s="21"/>
       <c r="D97" s="97"/>
@@ -21488,7 +21469,7 @@
       <c r="BM97" s="108"/>
       <c r="BN97" s="108"/>
     </row>
-    <row r="98" spans="2:66" ht="19.2" customHeight="1">
+    <row r="98" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B98" s="96"/>
       <c r="C98" s="21"/>
       <c r="D98" s="97"/>
@@ -21554,7 +21535,7 @@
       <c r="BM98" s="108"/>
       <c r="BN98" s="108"/>
     </row>
-    <row r="99" spans="2:66" ht="19.2" customHeight="1">
+    <row r="99" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B99" s="96"/>
       <c r="C99" s="21"/>
       <c r="D99" s="97"/>
@@ -21620,7 +21601,7 @@
       <c r="BM99" s="108"/>
       <c r="BN99" s="108"/>
     </row>
-    <row r="100" spans="2:66" ht="19.2" customHeight="1">
+    <row r="100" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B100" s="96"/>
       <c r="C100" s="21"/>
       <c r="D100" s="97"/>
@@ -21686,7 +21667,7 @@
       <c r="BM100" s="108"/>
       <c r="BN100" s="108"/>
     </row>
-    <row r="101" spans="2:66" ht="19.2" customHeight="1">
+    <row r="101" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B101" s="96"/>
       <c r="C101" s="21"/>
       <c r="D101" s="97"/>
@@ -21752,7 +21733,7 @@
       <c r="BM101" s="108"/>
       <c r="BN101" s="108"/>
     </row>
-    <row r="102" spans="2:66" ht="19.2" customHeight="1">
+    <row r="102" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B102" s="96"/>
       <c r="C102" s="21"/>
       <c r="D102" s="97"/>
@@ -21818,7 +21799,7 @@
       <c r="BM102" s="108"/>
       <c r="BN102" s="108"/>
     </row>
-    <row r="103" spans="2:66" ht="19.2" customHeight="1">
+    <row r="103" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B103" s="96"/>
       <c r="C103" s="21"/>
       <c r="D103" s="97"/>
@@ -21884,7 +21865,7 @@
       <c r="BM103" s="108"/>
       <c r="BN103" s="108"/>
     </row>
-    <row r="104" spans="2:66" ht="19.2" customHeight="1">
+    <row r="104" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B104" s="96"/>
       <c r="C104" s="21"/>
       <c r="D104" s="97"/>
@@ -21950,7 +21931,7 @@
       <c r="BM104" s="108"/>
       <c r="BN104" s="108"/>
     </row>
-    <row r="105" spans="2:66" ht="19.2" customHeight="1">
+    <row r="105" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B105" s="96"/>
       <c r="C105" s="21"/>
       <c r="D105" s="97"/>
@@ -22016,7 +21997,7 @@
       <c r="BM105" s="108"/>
       <c r="BN105" s="108"/>
     </row>
-    <row r="106" spans="2:66" ht="19.2" customHeight="1">
+    <row r="106" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B106" s="96"/>
       <c r="C106" s="21"/>
       <c r="D106" s="97"/>
@@ -22082,7 +22063,7 @@
       <c r="BM106" s="108"/>
       <c r="BN106" s="108"/>
     </row>
-    <row r="107" spans="2:66" ht="19.2" customHeight="1">
+    <row r="107" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B107" s="96"/>
       <c r="C107" s="21"/>
       <c r="D107" s="97"/>
@@ -22148,7 +22129,7 @@
       <c r="BM107" s="108"/>
       <c r="BN107" s="108"/>
     </row>
-    <row r="108" spans="2:66" ht="19.2" customHeight="1">
+    <row r="108" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B108" s="96"/>
       <c r="C108" s="21"/>
       <c r="D108" s="97"/>
@@ -22214,7 +22195,7 @@
       <c r="BM108" s="108"/>
       <c r="BN108" s="108"/>
     </row>
-    <row r="109" spans="2:66" ht="19.2" customHeight="1">
+    <row r="109" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B109" s="96"/>
       <c r="C109" s="21"/>
       <c r="D109" s="97"/>
@@ -22280,7 +22261,7 @@
       <c r="BM109" s="108"/>
       <c r="BN109" s="108"/>
     </row>
-    <row r="110" spans="2:66" ht="19.2" customHeight="1">
+    <row r="110" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B110" s="96"/>
       <c r="C110" s="21"/>
       <c r="D110" s="97"/>
@@ -22346,7 +22327,7 @@
       <c r="BM110" s="108"/>
       <c r="BN110" s="108"/>
     </row>
-    <row r="111" spans="2:66" ht="19.2" customHeight="1">
+    <row r="111" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B111" s="96"/>
       <c r="C111" s="21"/>
       <c r="D111" s="97"/>
@@ -22412,7 +22393,7 @@
       <c r="BM111" s="108"/>
       <c r="BN111" s="108"/>
     </row>
-    <row r="112" spans="2:66" ht="19.2" customHeight="1">
+    <row r="112" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B112" s="96"/>
       <c r="C112" s="21"/>
       <c r="D112" s="97"/>
@@ -22478,7 +22459,7 @@
       <c r="BM112" s="108"/>
       <c r="BN112" s="108"/>
     </row>
-    <row r="113" spans="2:66" ht="19.2" customHeight="1">
+    <row r="113" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B113" s="96"/>
       <c r="C113" s="21"/>
       <c r="D113" s="97"/>
@@ -22544,7 +22525,7 @@
       <c r="BM113" s="108"/>
       <c r="BN113" s="108"/>
     </row>
-    <row r="114" spans="2:66" ht="19.2" customHeight="1">
+    <row r="114" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B114" s="96"/>
       <c r="C114" s="21"/>
       <c r="D114" s="97"/>
@@ -22610,7 +22591,7 @@
       <c r="BM114" s="108"/>
       <c r="BN114" s="108"/>
     </row>
-    <row r="115" spans="2:66" ht="19.2" customHeight="1">
+    <row r="115" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B115" s="96"/>
       <c r="C115" s="21"/>
       <c r="D115" s="97"/>
@@ -22676,7 +22657,7 @@
       <c r="BM115" s="108"/>
       <c r="BN115" s="108"/>
     </row>
-    <row r="116" spans="2:66" ht="19.2" customHeight="1">
+    <row r="116" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B116" s="96"/>
       <c r="C116" s="21"/>
       <c r="D116" s="97"/>
@@ -22742,7 +22723,7 @@
       <c r="BM116" s="108"/>
       <c r="BN116" s="108"/>
     </row>
-    <row r="117" spans="2:66" ht="19.2" customHeight="1">
+    <row r="117" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B117" s="96"/>
       <c r="C117" s="21"/>
       <c r="D117" s="97"/>
@@ -22808,7 +22789,7 @@
       <c r="BM117" s="108"/>
       <c r="BN117" s="108"/>
     </row>
-    <row r="118" spans="2:66" ht="19.2" customHeight="1">
+    <row r="118" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B118" s="96"/>
       <c r="C118" s="21"/>
       <c r="D118" s="97"/>
@@ -22874,7 +22855,7 @@
       <c r="BM118" s="108"/>
       <c r="BN118" s="108"/>
     </row>
-    <row r="119" spans="2:66" ht="19.2" customHeight="1">
+    <row r="119" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B119" s="96"/>
       <c r="C119" s="21"/>
       <c r="D119" s="97"/>
@@ -22940,7 +22921,7 @@
       <c r="BM119" s="108"/>
       <c r="BN119" s="108"/>
     </row>
-    <row r="120" spans="2:66" ht="19.2" customHeight="1">
+    <row r="120" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B120" s="96"/>
       <c r="C120" s="21"/>
       <c r="D120" s="97"/>
@@ -23006,7 +22987,7 @@
       <c r="BM120" s="108"/>
       <c r="BN120" s="108"/>
     </row>
-    <row r="121" spans="2:66" ht="19.2" customHeight="1">
+    <row r="121" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B121" s="96"/>
       <c r="C121" s="21"/>
       <c r="D121" s="97"/>
@@ -23072,7 +23053,7 @@
       <c r="BM121" s="108"/>
       <c r="BN121" s="108"/>
     </row>
-    <row r="122" spans="2:66" ht="19.2" customHeight="1">
+    <row r="122" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B122" s="96"/>
       <c r="C122" s="21"/>
       <c r="D122" s="97"/>
@@ -23138,7 +23119,7 @@
       <c r="BM122" s="108"/>
       <c r="BN122" s="108"/>
     </row>
-    <row r="123" spans="2:66" ht="19.2" customHeight="1">
+    <row r="123" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B123" s="96"/>
       <c r="C123" s="21"/>
       <c r="D123" s="97"/>
@@ -23204,7 +23185,7 @@
       <c r="BM123" s="108"/>
       <c r="BN123" s="108"/>
     </row>
-    <row r="124" spans="2:66" ht="19.2" customHeight="1">
+    <row r="124" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B124" s="96"/>
       <c r="C124" s="21"/>
       <c r="D124" s="97"/>
@@ -23270,7 +23251,7 @@
       <c r="BM124" s="108"/>
       <c r="BN124" s="108"/>
     </row>
-    <row r="125" spans="2:66" ht="19.2" customHeight="1">
+    <row r="125" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B125" s="96"/>
       <c r="C125" s="21"/>
       <c r="D125" s="97"/>
@@ -23336,7 +23317,7 @@
       <c r="BM125" s="108"/>
       <c r="BN125" s="108"/>
     </row>
-    <row r="126" spans="2:66" ht="19.2" customHeight="1">
+    <row r="126" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B126" s="96"/>
       <c r="C126" s="21"/>
       <c r="D126" s="97"/>
@@ -23402,7 +23383,7 @@
       <c r="BM126" s="108"/>
       <c r="BN126" s="108"/>
     </row>
-    <row r="127" spans="2:66" ht="19.2" customHeight="1">
+    <row r="127" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B127" s="96"/>
       <c r="C127" s="21"/>
       <c r="D127" s="97"/>
@@ -23468,7 +23449,7 @@
       <c r="BM127" s="108"/>
       <c r="BN127" s="108"/>
     </row>
-    <row r="128" spans="2:66" ht="19.2" customHeight="1">
+    <row r="128" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B128" s="96"/>
       <c r="C128" s="21"/>
       <c r="D128" s="97"/>
@@ -23534,7 +23515,7 @@
       <c r="BM128" s="108"/>
       <c r="BN128" s="108"/>
     </row>
-    <row r="129" spans="2:66" ht="19.2" customHeight="1">
+    <row r="129" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B129" s="96"/>
       <c r="C129" s="21"/>
       <c r="D129" s="97"/>
@@ -23600,7 +23581,7 @@
       <c r="BM129" s="108"/>
       <c r="BN129" s="108"/>
     </row>
-    <row r="130" spans="2:66" ht="19.2" customHeight="1">
+    <row r="130" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B130" s="96"/>
       <c r="C130" s="21"/>
       <c r="D130" s="97"/>
@@ -23666,7 +23647,7 @@
       <c r="BM130" s="108"/>
       <c r="BN130" s="108"/>
     </row>
-    <row r="131" spans="2:66" ht="19.2" customHeight="1">
+    <row r="131" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B131" s="96"/>
       <c r="C131" s="21"/>
       <c r="D131" s="97"/>
@@ -23732,7 +23713,7 @@
       <c r="BM131" s="108"/>
       <c r="BN131" s="108"/>
     </row>
-    <row r="132" spans="2:66" ht="19.2" customHeight="1">
+    <row r="132" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B132" s="96"/>
       <c r="C132" s="21"/>
       <c r="D132" s="97"/>
@@ -23798,7 +23779,7 @@
       <c r="BM132" s="108"/>
       <c r="BN132" s="108"/>
     </row>
-    <row r="133" spans="2:66" ht="19.2" customHeight="1">
+    <row r="133" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B133" s="96"/>
       <c r="C133" s="21"/>
       <c r="D133" s="97"/>
@@ -23864,7 +23845,7 @@
       <c r="BM133" s="108"/>
       <c r="BN133" s="108"/>
     </row>
-    <row r="134" spans="2:66" ht="19.2" customHeight="1">
+    <row r="134" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B134" s="96"/>
       <c r="C134" s="21"/>
       <c r="D134" s="97"/>
@@ -23930,7 +23911,7 @@
       <c r="BM134" s="108"/>
       <c r="BN134" s="108"/>
     </row>
-    <row r="135" spans="2:66" ht="19.2" customHeight="1">
+    <row r="135" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B135" s="96"/>
       <c r="C135" s="21"/>
       <c r="D135" s="97"/>
@@ -23996,7 +23977,7 @@
       <c r="BM135" s="108"/>
       <c r="BN135" s="108"/>
     </row>
-    <row r="136" spans="2:66" ht="19.2" customHeight="1">
+    <row r="136" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B136" s="96"/>
       <c r="C136" s="21"/>
       <c r="D136" s="97"/>
@@ -24062,7 +24043,7 @@
       <c r="BM136" s="108"/>
       <c r="BN136" s="108"/>
     </row>
-    <row r="137" spans="2:66" ht="19.2" customHeight="1">
+    <row r="137" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B137" s="96"/>
       <c r="C137" s="21"/>
       <c r="D137" s="97"/>
@@ -24128,7 +24109,7 @@
       <c r="BM137" s="108"/>
       <c r="BN137" s="108"/>
     </row>
-    <row r="138" spans="2:66" ht="19.2" customHeight="1">
+    <row r="138" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B138" s="96"/>
       <c r="C138" s="21"/>
       <c r="D138" s="97"/>
@@ -24194,7 +24175,7 @@
       <c r="BM138" s="108"/>
       <c r="BN138" s="108"/>
     </row>
-    <row r="139" spans="2:66" ht="19.2" customHeight="1">
+    <row r="139" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B139" s="96"/>
       <c r="C139" s="21"/>
       <c r="D139" s="97"/>
@@ -24260,7 +24241,7 @@
       <c r="BM139" s="108"/>
       <c r="BN139" s="108"/>
     </row>
-    <row r="140" spans="2:66" ht="19.2" customHeight="1">
+    <row r="140" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B140" s="96"/>
       <c r="C140" s="21"/>
       <c r="D140" s="97"/>
@@ -24326,7 +24307,7 @@
       <c r="BM140" s="108"/>
       <c r="BN140" s="108"/>
     </row>
-    <row r="141" spans="2:66" ht="19.2" customHeight="1">
+    <row r="141" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B141" s="96"/>
       <c r="C141" s="21"/>
       <c r="D141" s="97"/>
@@ -24392,7 +24373,7 @@
       <c r="BM141" s="108"/>
       <c r="BN141" s="108"/>
     </row>
-    <row r="142" spans="2:66" ht="19.2" customHeight="1">
+    <row r="142" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B142" s="96"/>
       <c r="C142" s="21"/>
       <c r="D142" s="97"/>
@@ -24458,7 +24439,7 @@
       <c r="BM142" s="108"/>
       <c r="BN142" s="108"/>
     </row>
-    <row r="143" spans="2:66" ht="19.2" customHeight="1">
+    <row r="143" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B143" s="96"/>
       <c r="C143" s="21"/>
       <c r="D143" s="97"/>
@@ -24524,7 +24505,7 @@
       <c r="BM143" s="108"/>
       <c r="BN143" s="108"/>
     </row>
-    <row r="144" spans="2:66" ht="19.2" customHeight="1">
+    <row r="144" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B144" s="96"/>
       <c r="C144" s="21"/>
       <c r="D144" s="97"/>
@@ -24590,7 +24571,7 @@
       <c r="BM144" s="108"/>
       <c r="BN144" s="108"/>
     </row>
-    <row r="145" spans="2:66" ht="19.2" customHeight="1">
+    <row r="145" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B145" s="96"/>
       <c r="C145" s="21"/>
       <c r="D145" s="97"/>
